--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gshelton28\Documents\MATLAB\MBSE\ship-mbse\data\input_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB4C1E2D-5357-439F-8F0C-43B56C66282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5512CBF-DF7E-470A-A8F5-85EDC75619B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3360" windowWidth="29040" windowHeight="17520" xr2:uid="{98B5C58D-9CFA-4291-9996-C17FD3CE1B6B}"/>
+    <workbookView xWindow="-28920" yWindow="8595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,39 +27,212 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="96">
   <si>
     <t>Profile--&gt;</t>
   </si>
   <si>
+    <t>WeightsCentersProfile</t>
+  </si>
+  <si>
+    <t>ElectricalProfile</t>
+  </si>
+  <si>
+    <t>FuelProfile</t>
+  </si>
+  <si>
+    <t>CoolingProfile</t>
+  </si>
+  <si>
+    <t>LubeProfile</t>
+  </si>
+  <si>
+    <t>CompAirProfile</t>
+  </si>
+  <si>
+    <t>WasteProfile</t>
+  </si>
+  <si>
     <t>Stereotype--&gt;</t>
   </si>
   <si>
+    <t>WeightsCenters</t>
+  </si>
+  <si>
+    <t>ElectricalConsumer</t>
+  </si>
+  <si>
+    <t>ElectricalGenerator</t>
+  </si>
+  <si>
+    <t>FuelConsumer</t>
+  </si>
+  <si>
+    <t>FuelProducer</t>
+  </si>
+  <si>
+    <t>CoolConsumer</t>
+  </si>
+  <si>
+    <t>CoolProducer</t>
+  </si>
+  <si>
+    <t>LubeConsumer</t>
+  </si>
+  <si>
+    <t>LubeProducer</t>
+  </si>
+  <si>
+    <t>AirConsumer</t>
+  </si>
+  <si>
+    <t>AirProducer</t>
+  </si>
+  <si>
+    <t>WasteGasProducer</t>
+  </si>
+  <si>
+    <t>WasteSolidProducer</t>
+  </si>
+  <si>
+    <t>WasteWaterProducer</t>
+  </si>
+  <si>
+    <t>WasteOilProducer</t>
+  </si>
+  <si>
+    <t>WasteReceiver</t>
+  </si>
+  <si>
     <t>Property--&gt;</t>
   </si>
   <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>LCG</t>
+  </si>
+  <si>
+    <t>VCG</t>
+  </si>
+  <si>
+    <t>TCG</t>
+  </si>
+  <si>
+    <t>WeightMargin</t>
+  </si>
+  <si>
+    <t>PowerRequired</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>PowerGenerated</t>
+  </si>
+  <si>
+    <t>FuelRequired</t>
+  </si>
+  <si>
+    <t>FuelProduced</t>
+  </si>
+  <si>
+    <t>FuelStored</t>
+  </si>
+  <si>
+    <t>CoolConsumed</t>
+  </si>
+  <si>
+    <t>CoolProduced</t>
+  </si>
+  <si>
+    <t>LubeRequired</t>
+  </si>
+  <si>
+    <t>LubeProduced</t>
+  </si>
+  <si>
+    <t>AirConsumed</t>
+  </si>
+  <si>
+    <t>AirProduced</t>
+  </si>
+  <si>
+    <t>WGProduced</t>
+  </si>
+  <si>
+    <t>WSProduced</t>
+  </si>
+  <si>
+    <t>WWProduced</t>
+  </si>
+  <si>
+    <t>WOProduced</t>
+  </si>
+  <si>
+    <t>WGReceived</t>
+  </si>
+  <si>
+    <t>WSReceived</t>
+  </si>
+  <si>
+    <t>WWReceived</t>
+  </si>
+  <si>
+    <t>WOReceived</t>
+  </si>
+  <si>
     <t>Component</t>
   </si>
   <si>
+    <t>(t)</t>
+  </si>
+  <si>
+    <t>(m)</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>(kW)</t>
+  </si>
+  <si>
+    <t>On/Off</t>
+  </si>
+  <si>
+    <t>kL/s</t>
+  </si>
+  <si>
+    <t>kL</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>10X (PLATE)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>11X (FRAMING)</t>
   </si>
   <si>
-    <t>10X (PLATE)</t>
-  </si>
-  <si>
     <t>12X (STIFFENERS)</t>
   </si>
   <si>
+    <t>20X (MAIN ENGINE)</t>
+  </si>
+  <si>
     <t>21X (PROPULSORS)</t>
   </si>
   <si>
@@ -105,6 +278,9 @@
     <t>51X (LUBE OIL)</t>
   </si>
   <si>
+    <t>52X (FUEL)</t>
+  </si>
+  <si>
     <t>53X (COMPRESSED AIR)</t>
   </si>
   <si>
@@ -126,207 +302,39 @@
     <t>59X (HOTEL)</t>
   </si>
   <si>
+    <t>60X (ACCOMODATION)</t>
+  </si>
+  <si>
     <t>61X (SHOPS)</t>
   </si>
   <si>
     <t>62X (LSA)</t>
   </si>
   <si>
-    <t>60X (ACCOMODATION)</t>
-  </si>
-  <si>
     <t>70X (ASW)</t>
   </si>
   <si>
     <t>71X (SS)</t>
   </si>
   <si>
+    <t>72X (SA)</t>
+  </si>
+  <si>
     <t>73X (EW)</t>
   </si>
   <si>
     <t>74X (COUNTERMEASURES)</t>
-  </si>
-  <si>
-    <t>WeightsCentersProfile</t>
-  </si>
-  <si>
-    <t>WeightsCenters</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>LCG</t>
-  </si>
-  <si>
-    <t>VCG</t>
-  </si>
-  <si>
-    <t>TCG</t>
-  </si>
-  <si>
-    <t>(t)</t>
-  </si>
-  <si>
-    <t>(m)</t>
-  </si>
-  <si>
-    <t>ElectricalProfile</t>
-  </si>
-  <si>
-    <t>ElectricalConsumer</t>
-  </si>
-  <si>
-    <t>ElectricalGenerator</t>
-  </si>
-  <si>
-    <t>PowerRequired</t>
-  </si>
-  <si>
-    <t>(kW)</t>
-  </si>
-  <si>
-    <t>PowerGenerated</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>On/Off</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>20X (MAIN ENGINE)</t>
-  </si>
-  <si>
-    <t>72X (SA)</t>
-  </si>
-  <si>
-    <t>52X (FUEL)</t>
-  </si>
-  <si>
-    <t>FuelProfile</t>
-  </si>
-  <si>
-    <t>FuelConsumer</t>
-  </si>
-  <si>
-    <t>FuelRequired</t>
-  </si>
-  <si>
-    <t>FuelProducer</t>
-  </si>
-  <si>
-    <t>FuelProduced</t>
-  </si>
-  <si>
-    <t>FuelStored</t>
-  </si>
-  <si>
-    <t>kL/s</t>
-  </si>
-  <si>
-    <t>kL</t>
-  </si>
-  <si>
-    <t>CoolingProfile</t>
-  </si>
-  <si>
-    <t>CoolConsumer</t>
-  </si>
-  <si>
-    <t>CoolProducer</t>
-  </si>
-  <si>
-    <t>CoolConsumed</t>
-  </si>
-  <si>
-    <t>CoolProduced</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>WeightMargin</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>LubeProfile</t>
-  </si>
-  <si>
-    <t>LubeConsumer</t>
-  </si>
-  <si>
-    <t>LubeProducer</t>
-  </si>
-  <si>
-    <t>LubeRequired</t>
-  </si>
-  <si>
-    <t>LubeProduced</t>
-  </si>
-  <si>
-    <t>CompAirProfile</t>
-  </si>
-  <si>
-    <t>AirConsumer</t>
-  </si>
-  <si>
-    <t>AirProducer</t>
-  </si>
-  <si>
-    <t>AirConsumed</t>
-  </si>
-  <si>
-    <t>AirProduced</t>
-  </si>
-  <si>
-    <t>WasteProfile</t>
-  </si>
-  <si>
-    <t>WasteGasProducer</t>
-  </si>
-  <si>
-    <t>WasteSolidProducer</t>
-  </si>
-  <si>
-    <t>WasteWaterProducer</t>
-  </si>
-  <si>
-    <t>WGProduced</t>
-  </si>
-  <si>
-    <t>WSProduced</t>
-  </si>
-  <si>
-    <t>WWProduced</t>
-  </si>
-  <si>
-    <t>WasteReciever</t>
-  </si>
-  <si>
-    <t>WGRecieved</t>
-  </si>
-  <si>
-    <t>WSRecieved</t>
-  </si>
-  <si>
-    <t>WWRecieved</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -381,39 +389,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -446,26 +454,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -498,23 +489,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,6 +550,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -584,13 +565,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -655,652 +629,959 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A76AF4-A03A-4737-AA76-4B6EFB48ED33}">
-  <dimension ref="A1:AK39"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AN39"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="29.25" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
-    <col min="3" max="3" width="22.875" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="6" width="20.375" customWidth="1"/>
-    <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
-    <col min="9" max="9" width="22.375" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
-    <col min="11" max="11" width="18.125" customWidth="1"/>
-    <col min="12" max="12" width="14.25" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="16.5" customWidth="1"/>
-    <col min="17" max="17" width="15.625" customWidth="1"/>
-    <col min="18" max="18" width="14.5" customWidth="1"/>
-    <col min="19" max="19" width="13.75" customWidth="1"/>
-    <col min="20" max="20" width="15.625" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="22" width="15.375" customWidth="1"/>
-    <col min="23" max="23" width="13.75" customWidth="1"/>
-    <col min="24" max="24" width="13.5" customWidth="1"/>
-    <col min="25" max="25" width="13.625" customWidth="1"/>
-    <col min="26" max="26" width="14.125" customWidth="1"/>
-    <col min="27" max="27" width="14.25" customWidth="1"/>
-    <col min="28" max="28" width="17.875" customWidth="1"/>
-    <col min="29" max="29" width="17.375" customWidth="1"/>
-    <col min="30" max="31" width="18.125" customWidth="1"/>
-    <col min="32" max="32" width="19.875" customWidth="1"/>
-    <col min="33" max="33" width="18.875" customWidth="1"/>
-    <col min="34" max="34" width="15.25" customWidth="1"/>
-    <col min="35" max="35" width="14.875" customWidth="1"/>
-    <col min="36" max="36" width="15" customWidth="1"/>
-    <col min="37" max="37" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="29.7890625" customWidth="1"/>
+    <col min="2" max="2" width="21.89453125" customWidth="1"/>
+    <col min="3" max="3" width="22.9453125" customWidth="1"/>
+    <col min="4" max="4" width="22.68359375" customWidth="1"/>
+    <col min="5" max="5" width="21.3671875" customWidth="1"/>
+    <col min="6" max="6" width="22.41796875" customWidth="1"/>
+    <col min="7" max="7" width="15.41796875" customWidth="1"/>
+    <col min="8" max="8" width="16.62890625" customWidth="1"/>
+    <col min="9" max="9" width="19.7890625" customWidth="1"/>
+    <col min="10" max="10" width="14.62890625" customWidth="1"/>
+    <col min="11" max="11" width="15.41796875" customWidth="1"/>
+    <col min="12" max="12" width="18.20703125" customWidth="1"/>
+    <col min="13" max="13" width="15.41796875" customWidth="1"/>
+    <col min="14" max="14" width="19.7890625" customWidth="1"/>
+    <col min="15" max="15" width="14.89453125" customWidth="1"/>
+    <col min="16" max="16" width="13.734375" customWidth="1"/>
+    <col min="17" max="17" width="15.3125" customWidth="1"/>
+    <col min="18" max="18" width="13.83984375" customWidth="1"/>
+    <col min="19" max="19" width="16.20703125" customWidth="1"/>
+    <col min="20" max="20" width="13.83984375" customWidth="1"/>
+    <col min="21" max="21" width="14.20703125" customWidth="1"/>
+    <col min="22" max="22" width="14.5234375" customWidth="1"/>
+    <col min="23" max="23" width="13.734375" customWidth="1"/>
+    <col min="24" max="24" width="13.05078125" customWidth="1"/>
+    <col min="25" max="25" width="13.578125" customWidth="1"/>
+    <col min="26" max="26" width="15.05078125" customWidth="1"/>
+    <col min="27" max="27" width="15.578125" customWidth="1"/>
+    <col min="28" max="28" width="13.47265625" customWidth="1"/>
+    <col min="29" max="29" width="11.89453125" customWidth="1"/>
+    <col min="30" max="30" width="14.5234375" customWidth="1"/>
+    <col min="31" max="31" width="13.20703125" customWidth="1"/>
+    <col min="32" max="32" width="13.47265625" customWidth="1"/>
+    <col min="33" max="33" width="13.83984375" customWidth="1"/>
+    <col min="34" max="34" width="14.1015625" customWidth="1"/>
+    <col min="35" max="35" width="14.5234375" customWidth="1"/>
+    <col min="36" max="36" width="14.3671875" customWidth="1"/>
+    <col min="37" max="37" width="14.26171875" customWidth="1"/>
+    <col min="38" max="38" width="13.05078125" customWidth="1"/>
+    <col min="39" max="39" width="14.26171875" customWidth="1"/>
+    <col min="40" max="40" width="12.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>5</v>
+      </c>
+      <c r="V1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" t="s">
+        <v>17</v>
+      </c>
+      <c r="W2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="AE3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
         <v>56</v>
       </c>
-      <c r="L1" t="s">
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
         <v>56</v>
       </c>
-      <c r="M1" t="s">
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
         <v>56</v>
       </c>
-      <c r="N1" t="s">
+      <c r="M4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" t="s">
         <v>56</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" t="s">
         <v>56</v>
       </c>
-      <c r="P1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" t="s">
-        <v>64</v>
-      </c>
-      <c r="T1" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" t="s">
-        <v>72</v>
-      </c>
-      <c r="V1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W1" t="s">
-        <v>72</v>
-      </c>
-      <c r="X1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>82</v>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" t="s">
+        <v>56</v>
+      </c>
+      <c r="X4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" t="s">
-        <v>59</v>
-      </c>
-      <c r="N2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>65</v>
-      </c>
-      <c r="R2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S2" t="s">
-        <v>66</v>
-      </c>
-      <c r="T2" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" t="s">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>60</v>
-      </c>
-      <c r="N3" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" t="s">
-        <v>75</v>
-      </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" t="s">
-        <v>76</v>
-      </c>
-      <c r="W3" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>51</v>
-      </c>
-      <c r="R4" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" t="s">
-        <v>51</v>
-      </c>
-      <c r="T4" t="s">
-        <v>62</v>
-      </c>
-      <c r="U4" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" t="s">
-        <v>62</v>
-      </c>
-      <c r="W4" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
-      <c r="A5" t="s">
-        <v>5</v>
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN(10,1000)</f>
-        <v>284</v>
+        <v>374</v>
       </c>
       <c r="C5">
         <f ca="1">RANDBETWEEN(0,200)</f>
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <f ca="1">RANDBETWEEN(0,35)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <f ca="1">RANDBETWEEN(-10,10)</f>
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <f ca="1">RANDBETWEEN(0,20)</f>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5" t="s">
+        <v>61</v>
+      </c>
+      <c r="U5" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" t="s">
+        <v>61</v>
+      </c>
+      <c r="W5" t="s">
+        <v>61</v>
+      </c>
+      <c r="X5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <f t="shared" ref="B6:B39" ca="1" si="0">RANDBETWEEN(10,1000)</f>
-        <v>561</v>
+        <v>466</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C39" ca="1" si="1">RANDBETWEEN(0,200)</f>
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D39" ca="1" si="2">RANDBETWEEN(0,35)</f>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:E39" ca="1" si="3">RANDBETWEEN(-10,10)</f>
-        <v>8</v>
+        <v>-5</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:G39" ca="1" si="4">RANDBETWEEN(0,20)</f>
+        <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>61</v>
+      </c>
+      <c r="R6" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" t="s">
+        <v>61</v>
+      </c>
+      <c r="U6" t="s">
+        <v>61</v>
+      </c>
+      <c r="V6" t="s">
+        <v>61</v>
+      </c>
+      <c r="W6" t="s">
+        <v>61</v>
+      </c>
+      <c r="X6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>470</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S7" t="s">
+        <v>61</v>
+      </c>
+      <c r="T7" t="s">
+        <v>61</v>
+      </c>
+      <c r="U7" t="s">
+        <v>61</v>
+      </c>
+      <c r="V7" t="s">
+        <v>61</v>
+      </c>
+      <c r="W7" t="s">
+        <v>61</v>
+      </c>
+      <c r="X7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="0"/>
-        <v>885</v>
+        <v>975</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
       </c>
       <c r="G8">
-        <f t="shared" ref="G8:G38" ca="1" si="4">RANDBETWEEN(0,20)</f>
-        <v>19</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3</v>
       </c>
       <c r="H8" t="b">
         <f t="shared" ref="H8:H39" ca="1" si="5">IF(RANDBETWEEN(1,2)=1, TRUE, FALSE)</f>
@@ -1308,209 +1589,773 @@
       </c>
       <c r="I8">
         <f t="shared" ref="I8:I15" ca="1" si="6">RANDBETWEEN(100,200)</f>
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="J8" t="b">
         <f t="shared" ref="J8:J15" ca="1" si="7">IF(RANDBETWEEN(1,2)=1, TRUE, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
+        <v>61</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="s">
+        <v>61</v>
+      </c>
+      <c r="W8" t="s">
+        <v>61</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB8">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="0"/>
-        <v>454</v>
+        <v>614</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H9" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="6"/>
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="J9" t="b">
         <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
+      <c r="K9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
+        <v>61</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+      <c r="V9" t="s">
+        <v>61</v>
+      </c>
+      <c r="W9" t="s">
+        <v>61</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="0"/>
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>-6</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>61</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
+        <v>61</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" t="s">
+        <v>61</v>
+      </c>
+      <c r="W10" t="s">
+        <v>61</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="0"/>
-        <v>252</v>
+        <v>675</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="6"/>
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="J11" t="b">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" t="s">
+        <v>61</v>
+      </c>
+      <c r="P11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" t="s">
+        <v>61</v>
+      </c>
+      <c r="S11" t="s">
+        <v>61</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
+        <v>61</v>
+      </c>
+      <c r="W11" t="s">
+        <v>61</v>
+      </c>
+      <c r="X11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="0"/>
-        <v>234</v>
+        <v>535</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-10</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="6"/>
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="J12" t="b">
         <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
+      <c r="K12">
+        <v>15</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>61</v>
+      </c>
+      <c r="R12" t="s">
+        <v>61</v>
+      </c>
+      <c r="S12" t="s">
+        <v>61</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" t="s">
+        <v>61</v>
+      </c>
+      <c r="W12" t="s">
+        <v>61</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB12">
+        <v>6</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="0"/>
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>61</v>
+      </c>
+      <c r="R13" t="s">
+        <v>61</v>
+      </c>
+      <c r="S13" t="s">
+        <v>61</v>
+      </c>
+      <c r="T13" t="s">
+        <v>61</v>
+      </c>
+      <c r="U13" t="s">
+        <v>61</v>
+      </c>
+      <c r="V13" t="s">
+        <v>61</v>
+      </c>
+      <c r="W13" t="s">
+        <v>61</v>
+      </c>
+      <c r="X13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="0"/>
-        <v>814</v>
+        <v>68</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>-10</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ca="1" si="4"/>
+        <v>0</v>
       </c>
       <c r="G14">
         <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H14" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -1518,125 +2363,497 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="6"/>
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J14" t="b">
         <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
+      <c r="K14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" t="s">
+        <v>61</v>
+      </c>
+      <c r="P14" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>61</v>
+      </c>
+      <c r="R14" t="s">
+        <v>61</v>
+      </c>
+      <c r="S14" t="s">
+        <v>61</v>
+      </c>
+      <c r="T14" t="s">
+        <v>61</v>
+      </c>
+      <c r="U14" t="s">
+        <v>61</v>
+      </c>
+      <c r="V14" t="s">
+        <v>61</v>
+      </c>
+      <c r="W14" t="s">
+        <v>61</v>
+      </c>
+      <c r="X14" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="0"/>
-        <v>491</v>
+        <v>438</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="6"/>
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="J15" t="b">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" t="s">
+        <v>61</v>
+      </c>
+      <c r="P15" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" t="s">
+        <v>61</v>
+      </c>
+      <c r="T15" t="s">
+        <v>61</v>
+      </c>
+      <c r="U15" t="s">
+        <v>61</v>
+      </c>
+      <c r="V15" t="s">
+        <v>61</v>
+      </c>
+      <c r="W15" t="s">
+        <v>61</v>
+      </c>
+      <c r="X15" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="0"/>
-        <v>247</v>
+        <v>812</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
       </c>
       <c r="G16">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H16" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" t="s">
+        <v>61</v>
+      </c>
+      <c r="P16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>61</v>
+      </c>
+      <c r="R16" t="s">
+        <v>61</v>
+      </c>
+      <c r="S16" t="s">
+        <v>61</v>
+      </c>
+      <c r="T16" t="s">
+        <v>61</v>
+      </c>
+      <c r="U16" t="s">
+        <v>61</v>
+      </c>
+      <c r="V16" t="s">
+        <v>61</v>
+      </c>
+      <c r="W16" t="s">
+        <v>61</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="0"/>
-        <v>557</v>
+        <v>744</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ca="1" si="4"/>
+        <v>11</v>
       </c>
       <c r="G17">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K17" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" t="s">
+        <v>61</v>
+      </c>
+      <c r="P17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>61</v>
+      </c>
+      <c r="R17" t="s">
+        <v>61</v>
+      </c>
+      <c r="S17" t="s">
+        <v>61</v>
+      </c>
+      <c r="T17" t="s">
+        <v>61</v>
+      </c>
+      <c r="U17" t="s">
+        <v>61</v>
+      </c>
+      <c r="V17" t="s">
+        <v>61</v>
+      </c>
+      <c r="W17" t="s">
+        <v>61</v>
+      </c>
+      <c r="X17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="0"/>
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
@@ -1644,563 +2861,2067 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>-6</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ca="1" si="4"/>
+        <v>18</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H18" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" t="s">
+        <v>61</v>
+      </c>
+      <c r="O18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>61</v>
+      </c>
+      <c r="S18" t="s">
+        <v>61</v>
+      </c>
+      <c r="T18" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" t="s">
+        <v>61</v>
+      </c>
+      <c r="V18" t="s">
+        <v>61</v>
+      </c>
+      <c r="W18" t="s">
+        <v>61</v>
+      </c>
+      <c r="X18" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="0"/>
-        <v>639</v>
+        <v>752</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f t="shared" ca="1" si="4"/>
+        <v>17</v>
       </c>
       <c r="G19">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H19" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" t="s">
+        <v>61</v>
+      </c>
+      <c r="O19" t="s">
+        <v>61</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="s">
+        <v>61</v>
+      </c>
+      <c r="S19" t="s">
+        <v>61</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
+        <v>61</v>
+      </c>
+      <c r="W19" t="s">
+        <v>61</v>
+      </c>
+      <c r="X19" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="0"/>
-        <v>385</v>
+        <v>893</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G20">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K20" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" t="s">
+        <v>61</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="s">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
+        <v>61</v>
+      </c>
+      <c r="T20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20" t="s">
+        <v>61</v>
+      </c>
+      <c r="V20" t="s">
+        <v>61</v>
+      </c>
+      <c r="W20" t="s">
+        <v>61</v>
+      </c>
+      <c r="X20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="0"/>
-        <v>743</v>
+        <v>928</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="4"/>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H21" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J21" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K21" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" t="s">
+        <v>61</v>
+      </c>
+      <c r="P21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R21" t="s">
+        <v>61</v>
+      </c>
+      <c r="S21" t="s">
+        <v>61</v>
+      </c>
+      <c r="T21" t="s">
+        <v>61</v>
+      </c>
+      <c r="U21" t="s">
+        <v>61</v>
+      </c>
+      <c r="V21" t="s">
+        <v>61</v>
+      </c>
+      <c r="W21" t="s">
+        <v>61</v>
+      </c>
+      <c r="X21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="0"/>
-        <v>872</v>
+        <v>430</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ca="1" si="4"/>
         <v>8</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H22" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K22" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" t="s">
+        <v>61</v>
+      </c>
+      <c r="O22" t="s">
+        <v>61</v>
+      </c>
+      <c r="P22" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>61</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="s">
+        <v>61</v>
+      </c>
+      <c r="W22" t="s">
+        <v>61</v>
+      </c>
+      <c r="X22" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="0"/>
-        <v>896</v>
+        <v>606</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>-1</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ca="1" si="4"/>
+        <v>19</v>
       </c>
       <c r="G23">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H23" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" t="s">
+        <v>61</v>
+      </c>
+      <c r="N23" t="s">
+        <v>61</v>
+      </c>
+      <c r="O23" t="s">
+        <v>61</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="s">
+        <v>61</v>
+      </c>
+      <c r="S23" t="s">
+        <v>61</v>
+      </c>
+      <c r="T23" t="s">
+        <v>61</v>
+      </c>
+      <c r="U23" t="s">
+        <v>61</v>
+      </c>
+      <c r="V23" t="s">
+        <v>61</v>
+      </c>
+      <c r="W23" t="s">
+        <v>61</v>
+      </c>
+      <c r="X23" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH23">
+        <v>8</v>
+      </c>
+      <c r="AI23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="0"/>
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="3"/>
         <v>9</v>
       </c>
+      <c r="F24">
+        <f t="shared" ca="1" si="4"/>
+        <v>14</v>
+      </c>
       <c r="G24">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H24" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K24" t="s">
+        <v>61</v>
+      </c>
+      <c r="L24" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24">
+        <v>100</v>
+      </c>
+      <c r="N24">
+        <v>10000</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="s">
+        <v>61</v>
+      </c>
+      <c r="S24" t="s">
+        <v>61</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="s">
+        <v>61</v>
+      </c>
+      <c r="W24" t="s">
+        <v>61</v>
+      </c>
+      <c r="X24" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH24">
+        <v>11</v>
+      </c>
+      <c r="AI24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="0"/>
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>-2</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ca="1" si="4"/>
+        <v>13</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H25" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K25" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" t="s">
+        <v>61</v>
+      </c>
+      <c r="O25" t="s">
+        <v>61</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="s">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
+        <v>61</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="s">
+        <v>61</v>
+      </c>
+      <c r="W25" t="s">
+        <v>61</v>
+      </c>
+      <c r="X25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z25">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="0"/>
-        <v>484</v>
+        <v>163</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
       <c r="G26">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H26" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" t="s">
+        <v>61</v>
+      </c>
+      <c r="O26" t="s">
+        <v>61</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="s">
+        <v>61</v>
+      </c>
+      <c r="S26" t="s">
+        <v>61</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="s">
+        <v>61</v>
+      </c>
+      <c r="W26" t="s">
+        <v>61</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="0"/>
-        <v>262</v>
+        <v>913</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="1"/>
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>-6</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J27" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K27">
+        <v>12</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" t="s">
+        <v>61</v>
+      </c>
+      <c r="O27" t="s">
+        <v>61</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="s">
+        <v>61</v>
+      </c>
+      <c r="S27" t="s">
+        <v>61</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="s">
+        <v>61</v>
+      </c>
+      <c r="W27" t="s">
+        <v>61</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF27">
+        <v>6</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="0"/>
-        <v>345</v>
+        <v>862</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="1"/>
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
       <c r="G28">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H28" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K28" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" t="s">
+        <v>61</v>
+      </c>
+      <c r="O28" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>61</v>
+      </c>
+      <c r="R28" t="s">
+        <v>61</v>
+      </c>
+      <c r="S28" t="s">
+        <v>61</v>
+      </c>
+      <c r="T28" t="s">
+        <v>61</v>
+      </c>
+      <c r="U28" t="s">
+        <v>61</v>
+      </c>
+      <c r="V28">
+        <v>50</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="0"/>
-        <v>470</v>
+        <v>321</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>-2</v>
+      </c>
+      <c r="F29">
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
       </c>
       <c r="G29">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H29" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J29" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K29" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" t="s">
+        <v>61</v>
+      </c>
+      <c r="O29" t="s">
+        <v>61</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="s">
+        <v>61</v>
+      </c>
+      <c r="S29" t="s">
+        <v>61</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>61</v>
+      </c>
+      <c r="W29" t="s">
+        <v>61</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ29">
+        <v>25</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL29">
+        <v>25</v>
+      </c>
+      <c r="AM29">
+        <v>25</v>
+      </c>
+      <c r="AN29">
+        <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="0"/>
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-10</v>
+      </c>
+      <c r="F30">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H30" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K30" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" t="s">
+        <v>61</v>
+      </c>
+      <c r="M30" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30" t="s">
+        <v>61</v>
+      </c>
+      <c r="O30" t="s">
+        <v>61</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="s">
+        <v>61</v>
+      </c>
+      <c r="S30" t="s">
+        <v>61</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>61</v>
+      </c>
+      <c r="W30" t="s">
+        <v>61</v>
+      </c>
+      <c r="X30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="0"/>
-        <v>170</v>
+        <v>641</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>5</v>
+      </c>
+      <c r="F31">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
       </c>
       <c r="G31">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H31" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" t="s">
+        <v>61</v>
+      </c>
+      <c r="O31" t="s">
+        <v>61</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="s">
+        <v>61</v>
+      </c>
+      <c r="S31" t="s">
+        <v>61</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="s">
+        <v>61</v>
+      </c>
+      <c r="W31" t="s">
+        <v>61</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF31">
+        <v>8</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="0"/>
-        <v>434</v>
+        <v>782</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>-7</v>
+      </c>
+      <c r="F32">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
       </c>
       <c r="G32">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H32" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" t="s">
+        <v>61</v>
+      </c>
+      <c r="O32" t="s">
+        <v>61</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="s">
+        <v>61</v>
+      </c>
+      <c r="S32" t="s">
+        <v>61</v>
+      </c>
+      <c r="T32" t="s">
+        <v>61</v>
+      </c>
+      <c r="U32" t="s">
+        <v>61</v>
+      </c>
+      <c r="V32" t="s">
+        <v>61</v>
+      </c>
+      <c r="W32" t="s">
+        <v>61</v>
+      </c>
+      <c r="X32" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD32">
+        <v>9</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF32">
+        <v>9</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B33">
         <f t="shared" ca="1" si="0"/>
-        <v>446</v>
+        <v>761</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-1</v>
+      </c>
+      <c r="F33">
+        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H33" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K33" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" t="s">
+        <v>61</v>
+      </c>
+      <c r="O33" t="s">
+        <v>61</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="s">
+        <v>61</v>
+      </c>
+      <c r="S33" t="s">
+        <v>61</v>
+      </c>
+      <c r="T33" t="s">
+        <v>61</v>
+      </c>
+      <c r="U33" t="s">
+        <v>61</v>
+      </c>
+      <c r="V33" t="s">
+        <v>61</v>
+      </c>
+      <c r="W33" t="s">
+        <v>61</v>
+      </c>
+      <c r="X33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD33">
+        <v>7</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF33">
+        <v>3</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="B34">
         <f t="shared" ca="1" si="0"/>
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="D34">
         <f t="shared" ca="1" si="2"/>
@@ -2208,196 +4929,760 @@
       </c>
       <c r="E34">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
       <c r="G34">
         <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H34" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K34" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" t="s">
+        <v>61</v>
+      </c>
+      <c r="O34" t="s">
+        <v>61</v>
+      </c>
+      <c r="P34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>61</v>
+      </c>
+      <c r="R34" t="s">
+        <v>61</v>
+      </c>
+      <c r="S34" t="s">
+        <v>61</v>
+      </c>
+      <c r="T34" t="s">
+        <v>61</v>
+      </c>
+      <c r="U34" t="s">
+        <v>61</v>
+      </c>
+      <c r="V34" t="s">
+        <v>61</v>
+      </c>
+      <c r="W34" t="s">
+        <v>61</v>
+      </c>
+      <c r="X34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="B35">
         <f t="shared" ca="1" si="0"/>
-        <v>643</v>
+        <v>151</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="1"/>
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="D35">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E35">
         <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
       <c r="G35">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H35" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J35" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K35" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" t="s">
+        <v>61</v>
+      </c>
+      <c r="O35" t="s">
+        <v>61</v>
+      </c>
+      <c r="P35" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>61</v>
+      </c>
+      <c r="R35" t="s">
+        <v>61</v>
+      </c>
+      <c r="S35" t="s">
+        <v>61</v>
+      </c>
+      <c r="T35" t="s">
+        <v>61</v>
+      </c>
+      <c r="U35" t="s">
+        <v>61</v>
+      </c>
+      <c r="V35" t="s">
+        <v>61</v>
+      </c>
+      <c r="W35" t="s">
+        <v>61</v>
+      </c>
+      <c r="X35" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="B36">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>-2</v>
+      </c>
+      <c r="F36">
+        <f t="shared" ca="1" si="4"/>
+        <v>17</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H36" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J36" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" t="s">
+        <v>61</v>
+      </c>
+      <c r="O36" t="s">
+        <v>61</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>61</v>
+      </c>
+      <c r="S36" t="s">
+        <v>61</v>
+      </c>
+      <c r="T36" t="s">
+        <v>61</v>
+      </c>
+      <c r="U36" t="s">
+        <v>61</v>
+      </c>
+      <c r="V36" t="s">
+        <v>61</v>
+      </c>
+      <c r="W36" t="s">
+        <v>61</v>
+      </c>
+      <c r="X36" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="B37">
         <f t="shared" ca="1" si="0"/>
-        <v>191</v>
+        <v>384</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="D37">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>-3</v>
+      </c>
+      <c r="F37">
+        <f t="shared" ca="1" si="4"/>
+        <v>14</v>
       </c>
       <c r="G37">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H37" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J37" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K37" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" t="s">
+        <v>61</v>
+      </c>
+      <c r="M37" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" t="s">
+        <v>61</v>
+      </c>
+      <c r="O37" t="s">
+        <v>61</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="s">
+        <v>61</v>
+      </c>
+      <c r="S37" t="s">
+        <v>61</v>
+      </c>
+      <c r="T37" t="s">
+        <v>61</v>
+      </c>
+      <c r="U37" t="s">
+        <v>61</v>
+      </c>
+      <c r="V37" t="s">
+        <v>61</v>
+      </c>
+      <c r="W37" t="s">
+        <v>61</v>
+      </c>
+      <c r="X37" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="B38">
         <f t="shared" ca="1" si="0"/>
-        <v>787</v>
+        <v>261</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E38">
         <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>-7</v>
+      </c>
+      <c r="F38">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
       </c>
       <c r="G38">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H38" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K38" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O38" t="s">
+        <v>61</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="s">
+        <v>61</v>
+      </c>
+      <c r="S38" t="s">
+        <v>61</v>
+      </c>
+      <c r="T38" t="s">
+        <v>61</v>
+      </c>
+      <c r="U38" t="s">
+        <v>61</v>
+      </c>
+      <c r="V38" t="s">
+        <v>61</v>
+      </c>
+      <c r="W38" t="s">
+        <v>61</v>
+      </c>
+      <c r="X38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B39">
         <f t="shared" ca="1" si="0"/>
-        <v>185</v>
+        <v>359</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <f t="shared" ca="1" si="4"/>
+        <v>9</v>
       </c>
       <c r="G39">
         <f ca="1">RANDBETWEEN(0,20)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H39" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J39" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="K39" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" t="s">
+        <v>61</v>
+      </c>
+      <c r="O39" t="s">
+        <v>61</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="s">
+        <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>61</v>
+      </c>
+      <c r="T39" t="s">
+        <v>61</v>
+      </c>
+      <c r="U39" t="s">
+        <v>61</v>
+      </c>
+      <c r="V39" t="s">
+        <v>61</v>
+      </c>
+      <c r="W39" t="s">
+        <v>61</v>
+      </c>
+      <c r="X39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5512CBF-DF7E-470A-A8F5-85EDC75619B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34737C0-73B2-42DE-A97F-1E3891B820EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="8595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="96">
   <si>
     <t>Profile--&gt;</t>
   </si>
@@ -1180,23 +1180,23 @@
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN(10,1000)</f>
-        <v>374</v>
+        <v>529</v>
       </c>
       <c r="C5">
         <f ca="1">RANDBETWEEN(0,200)</f>
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <f ca="1">RANDBETWEEN(0,35)</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <f ca="1">RANDBETWEEN(-10,10)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <f ca="1">RANDBETWEEN(0,20)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
         <v>61</v>
@@ -1307,23 +1307,23 @@
       </c>
       <c r="B6">
         <f t="shared" ref="B6:B39" ca="1" si="0">RANDBETWEEN(10,1000)</f>
-        <v>466</v>
+        <v>526</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:C39" ca="1" si="1">RANDBETWEEN(0,200)</f>
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D39" ca="1" si="2">RANDBETWEEN(0,35)</f>
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:E39" ca="1" si="3">RANDBETWEEN(-10,10)</f>
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:G39" ca="1" si="4">RANDBETWEEN(0,20)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
         <v>61</v>
@@ -1434,23 +1434,23 @@
       </c>
       <c r="B7">
         <f t="shared" ca="1" si="0"/>
-        <v>470</v>
+        <v>693</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
         <v>61</v>
@@ -1561,38 +1561,37 @@
       </c>
       <c r="B8">
         <f t="shared" ca="1" si="0"/>
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" ca="1" si="4"/>
         <v>7</v>
-      </c>
-      <c r="G8">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
       </c>
       <c r="H8" t="b">
         <f t="shared" ref="H8:H39" ca="1" si="5">IF(RANDBETWEEN(1,2)=1, TRUE, FALSE)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" ref="I8:I15" ca="1" si="6">RANDBETWEEN(100,200)</f>
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="J8" t="b">
-        <f t="shared" ref="J8:J15" ca="1" si="7">IF(RANDBETWEEN(1,2)=1, TRUE, FALSE)</f>
         <v>1</v>
       </c>
       <c r="K8">
@@ -1692,39 +1691,37 @@
       </c>
       <c r="B9">
         <f t="shared" ca="1" si="0"/>
-        <v>614</v>
+        <v>668</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="3"/>
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H9" t="b">
         <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
-      <c r="I9">
-        <f t="shared" ca="1" si="6"/>
-        <v>148</v>
-      </c>
-      <c r="J9" t="b">
-        <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
       </c>
       <c r="K9" t="s">
         <v>61</v>
@@ -1823,23 +1820,23 @@
       </c>
       <c r="B10">
         <f t="shared" ca="1" si="0"/>
-        <v>849</v>
+        <v>822</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>61</v>
@@ -1950,23 +1947,23 @@
       </c>
       <c r="B11">
         <f t="shared" ca="1" si="0"/>
-        <v>675</v>
+        <v>747</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
         <v>61</v>
@@ -1976,11 +1973,10 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="6"/>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J11" t="b">
-        <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
         <v>61</v>
@@ -2079,23 +2075,23 @@
       </c>
       <c r="B12">
         <f t="shared" ca="1" si="0"/>
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>61</v>
@@ -2105,10 +2101,9 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="6"/>
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="J12" t="b">
-        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="K12">
@@ -2208,23 +2203,23 @@
       </c>
       <c r="B13">
         <f t="shared" ca="1" si="0"/>
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="3"/>
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
         <v>61</v>
@@ -2335,27 +2330,27 @@
       </c>
       <c r="B14">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>956</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H14" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -2363,10 +2358,9 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="6"/>
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="J14" t="b">
-        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="K14" t="s">
@@ -2466,23 +2460,23 @@
       </c>
       <c r="B15">
         <f t="shared" ca="1" si="0"/>
-        <v>438</v>
+        <v>661</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -2492,10 +2486,9 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="6"/>
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="J15" t="b">
-        <f t="shared" ca="1" si="7"/>
         <v>1</v>
       </c>
       <c r="K15" t="s">
@@ -2595,11 +2588,11 @@
       </c>
       <c r="B16">
         <f t="shared" ca="1" si="0"/>
-        <v>812</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="2"/>
@@ -2607,11 +2600,11 @@
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <f t="shared" ca="1" si="4"/>
@@ -2619,7 +2612,7 @@
       </c>
       <c r="H16" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>61</v>
@@ -2724,31 +2717,31 @@
       </c>
       <c r="B17">
         <f t="shared" ca="1" si="0"/>
-        <v>744</v>
+        <v>139</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="2"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G17">
         <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H17" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="s">
         <v>61</v>
@@ -2853,27 +2846,27 @@
       </c>
       <c r="B18">
         <f t="shared" ca="1" si="0"/>
-        <v>987</v>
+        <v>185</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="2"/>
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -2982,27 +2975,27 @@
       </c>
       <c r="B19">
         <f t="shared" ca="1" si="0"/>
-        <v>752</v>
+        <v>342</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>197</v>
+        <v>40</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G19">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H19" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -3111,27 +3104,27 @@
       </c>
       <c r="B20">
         <f t="shared" ca="1" si="0"/>
-        <v>893</v>
+        <v>371</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -3240,27 +3233,27 @@
       </c>
       <c r="B21">
         <f t="shared" ca="1" si="0"/>
-        <v>928</v>
+        <v>176</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="1"/>
-        <v>187</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="3"/>
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H21" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -3369,23 +3362,23 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="0"/>
-        <v>430</v>
+        <v>559</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="1"/>
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="4"/>
@@ -3498,31 +3491,31 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="0"/>
-        <v>606</v>
+        <v>172</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="1"/>
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H23" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
         <v>61</v>
@@ -3627,31 +3620,31 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="0"/>
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H24" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
         <v>61</v>
@@ -3756,27 +3749,27 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="0"/>
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="2"/>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H25" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -3885,31 +3878,31 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="0"/>
-        <v>163</v>
+        <v>943</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="2"/>
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H26" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
         <v>61</v>
@@ -4014,15 +4007,15 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="0"/>
-        <v>913</v>
+        <v>803</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="1"/>
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="3"/>
@@ -4030,11 +4023,11 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H27" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -4143,31 +4136,31 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="0"/>
-        <v>862</v>
+        <v>895</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="F28">
         <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
         <v>61</v>
@@ -4272,31 +4265,31 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="0"/>
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="F29">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G29">
         <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H29" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="s">
         <v>61</v>
@@ -4401,27 +4394,27 @@
       </c>
       <c r="B30">
         <f t="shared" ca="1" si="0"/>
-        <v>896</v>
+        <v>119</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="1"/>
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="3"/>
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H30" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -4530,31 +4523,31 @@
       </c>
       <c r="B31">
         <f t="shared" ca="1" si="0"/>
-        <v>641</v>
+        <v>505</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="1"/>
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -4659,27 +4652,27 @@
       </c>
       <c r="B32">
         <f t="shared" ca="1" si="0"/>
-        <v>782</v>
+        <v>99</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="1"/>
-        <v>155</v>
+        <v>56</v>
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="F32">
         <f t="shared" ca="1" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ca="1" si="4"/>
         <v>15</v>
-      </c>
-      <c r="G32">
-        <f t="shared" ca="1" si="4"/>
-        <v>17</v>
       </c>
       <c r="H32" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -4788,31 +4781,31 @@
       </c>
       <c r="B33">
         <f t="shared" ca="1" si="0"/>
-        <v>761</v>
+        <v>457</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="1"/>
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="2"/>
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <f t="shared" ca="1" si="4"/>
         <v>15</v>
-      </c>
-      <c r="G33">
-        <f t="shared" ca="1" si="4"/>
-        <v>16</v>
       </c>
       <c r="H33" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
         <v>61</v>
@@ -4917,27 +4910,27 @@
       </c>
       <c r="B34">
         <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <v>712</v>
       </c>
       <c r="C34">
         <f t="shared" ca="1" si="1"/>
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="D34">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H34" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -5046,27 +5039,27 @@
       </c>
       <c r="B35">
         <f t="shared" ca="1" si="0"/>
-        <v>151</v>
+        <v>421</v>
       </c>
       <c r="C35">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E35">
         <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H35" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -5175,27 +5168,27 @@
       </c>
       <c r="B36">
         <f t="shared" ca="1" si="0"/>
-        <v>300</v>
+        <v>660</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="3"/>
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H36" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -5304,15 +5297,15 @@
       </c>
       <c r="B37">
         <f t="shared" ca="1" si="0"/>
-        <v>384</v>
+        <v>678</v>
       </c>
       <c r="C37">
         <f t="shared" ca="1" si="1"/>
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="D37">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E37">
         <f t="shared" ca="1" si="3"/>
@@ -5320,11 +5313,11 @@
       </c>
       <c r="F37">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G37">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H37" t="b">
         <f t="shared" ca="1" si="5"/>
@@ -5433,31 +5426,31 @@
       </c>
       <c r="B38">
         <f t="shared" ca="1" si="0"/>
-        <v>261</v>
+        <v>451</v>
       </c>
       <c r="C38">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D38">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E38">
         <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="F38">
         <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H38" t="b">
         <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="s">
         <v>61</v>
@@ -5562,27 +5555,27 @@
       </c>
       <c r="B39">
         <f t="shared" ca="1" si="0"/>
-        <v>359</v>
+        <v>253</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <f ca="1">RANDBETWEEN(0,20)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H39" t="b">
         <f t="shared" ca="1" si="5"/>

--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34737C0-73B2-42DE-A97F-1E3891B820EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9749B5D6-F3CB-4819-A3EA-E6F2D20CF4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="8595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="101">
   <si>
     <t>Profile--&gt;</t>
   </si>
@@ -324,6 +324,21 @@
   </si>
   <si>
     <t>74X (COUNTERMEASURES)</t>
+  </si>
+  <si>
+    <t>HeatProfile</t>
+  </si>
+  <si>
+    <t>HeatConsumer</t>
+  </si>
+  <si>
+    <t>HeatProducer</t>
+  </si>
+  <si>
+    <t>HeatProduced</t>
+  </si>
+  <si>
+    <t>HeatConsumed</t>
   </si>
 </sst>
 </file>
@@ -641,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AR39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="29.7890625" customWidth="1"/>
@@ -684,9 +699,13 @@
     <col min="38" max="38" width="13.05078125" customWidth="1"/>
     <col min="39" max="39" width="14.26171875" customWidth="1"/>
     <col min="40" max="40" width="12.9453125" customWidth="1"/>
+    <col min="41" max="41" width="13.05078125" customWidth="1"/>
+    <col min="42" max="42" width="15.9453125" customWidth="1"/>
+    <col min="43" max="43" width="16.62890625" customWidth="1"/>
+    <col min="44" max="44" width="12.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -807,8 +826,20 @@
       <c r="AN1" t="s">
         <v>7</v>
       </c>
+      <c r="AO1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -929,8 +960,20 @@
       <c r="AN2" t="s">
         <v>24</v>
       </c>
+      <c r="AO2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1051,8 +1094,20 @@
       <c r="AN3" t="s">
         <v>50</v>
       </c>
+      <c r="AO3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -1173,31 +1228,38 @@
       <c r="AN4" t="s">
         <v>57</v>
       </c>
+      <c r="AO4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>60</v>
       </c>
       <c r="B5">
-        <f ca="1">RANDBETWEEN(10,1000)</f>
-        <v>529</v>
+        <v>682</v>
       </c>
       <c r="C5">
-        <f ca="1">RANDBETWEEN(0,200)</f>
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D5">
-        <f ca="1">RANDBETWEEN(0,35)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <f ca="1">RANDBETWEEN(-10,10)</f>
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <f ca="1">RANDBETWEEN(0,20)</f>
-        <v>14</v>
-      </c>
       <c r="G5" t="s">
         <v>61</v>
       </c>
@@ -1300,31 +1362,38 @@
       <c r="AN5" t="s">
         <v>61</v>
       </c>
+      <c r="AO5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>62</v>
       </c>
       <c r="B6">
-        <f t="shared" ref="B6:B39" ca="1" si="0">RANDBETWEEN(10,1000)</f>
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:C39" ca="1" si="1">RANDBETWEEN(0,200)</f>
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D6">
-        <f t="shared" ref="D6:D39" ca="1" si="2">RANDBETWEEN(0,35)</f>
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>-4</v>
+      </c>
+      <c r="F6">
         <v>20</v>
       </c>
-      <c r="E6">
-        <f t="shared" ref="E6:E39" ca="1" si="3">RANDBETWEEN(-10,10)</f>
-        <v>-7</v>
-      </c>
-      <c r="F6">
-        <f t="shared" ref="F6:G39" ca="1" si="4">RANDBETWEEN(0,20)</f>
-        <v>18</v>
-      </c>
       <c r="G6" t="s">
         <v>61</v>
       </c>
@@ -1427,30 +1496,37 @@
       <c r="AN6" t="s">
         <v>61</v>
       </c>
+      <c r="AO6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>63</v>
       </c>
       <c r="B7">
-        <f t="shared" ca="1" si="0"/>
-        <v>693</v>
+        <v>193</v>
       </c>
       <c r="C7">
-        <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G7" t="s">
         <v>61</v>
@@ -1554,42 +1630,46 @@
       <c r="AN7" t="s">
         <v>61</v>
       </c>
+      <c r="AO7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>64</v>
       </c>
       <c r="B8">
-        <f t="shared" ca="1" si="0"/>
-        <v>983</v>
+        <v>423</v>
       </c>
       <c r="C8">
-        <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H8" t="b">
-        <f t="shared" ref="H8:H39" ca="1" si="5">IF(RANDBETWEEN(1,2)=1, TRUE, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <f t="shared" ref="I8:I15" ca="1" si="6">RANDBETWEEN(100,200)</f>
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1684,37 +1764,42 @@
       <c r="AN8" t="s">
         <v>61</v>
       </c>
+      <c r="AO8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>65</v>
       </c>
       <c r="B9">
-        <f t="shared" ca="1" si="0"/>
-        <v>668</v>
+        <v>198</v>
       </c>
       <c r="C9">
-        <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="D9">
-        <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H9" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="I9" t="s">
@@ -1813,30 +1898,37 @@
       <c r="AN9" t="s">
         <v>61</v>
       </c>
+      <c r="AO9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>66</v>
       </c>
       <c r="B10">
-        <f t="shared" ca="1" si="0"/>
-        <v>822</v>
+        <v>563</v>
       </c>
       <c r="C10">
-        <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="D10">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <f t="shared" ca="1" si="3"/>
         <v>8</v>
       </c>
       <c r="F10">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
         <v>61</v>
@@ -1940,30 +2032,37 @@
       <c r="AN10" t="s">
         <v>61</v>
       </c>
+      <c r="AO10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>67</v>
       </c>
       <c r="B11">
-        <f t="shared" ca="1" si="0"/>
-        <v>747</v>
+        <v>119</v>
       </c>
       <c r="C11">
-        <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D11">
-        <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E11">
-        <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F11">
-        <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G11" t="s">
         <v>61</v>
@@ -1972,8 +2071,7 @@
         <v>61</v>
       </c>
       <c r="I11">
-        <f t="shared" ca="1" si="6"/>
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2068,30 +2166,37 @@
       <c r="AN11" t="s">
         <v>61</v>
       </c>
+      <c r="AO11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>68</v>
       </c>
       <c r="B12">
-        <f t="shared" ca="1" si="0"/>
-        <v>557</v>
+        <v>441</v>
       </c>
       <c r="C12">
-        <f t="shared" ca="1" si="1"/>
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="D12">
-        <f t="shared" ca="1" si="2"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="F12">
-        <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
         <v>61</v>
@@ -2100,8 +2205,7 @@
         <v>61</v>
       </c>
       <c r="I12">
-        <f t="shared" ca="1" si="6"/>
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2196,30 +2300,37 @@
       <c r="AN12" t="s">
         <v>61</v>
       </c>
+      <c r="AO12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>69</v>
       </c>
       <c r="B13">
-        <f t="shared" ca="1" si="0"/>
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="C13">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
         <v>61</v>
@@ -2323,42 +2434,46 @@
       <c r="AN13" t="s">
         <v>61</v>
       </c>
+      <c r="AO13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>70</v>
       </c>
       <c r="B14">
-        <f t="shared" ca="1" si="0"/>
-        <v>956</v>
+        <v>867</v>
       </c>
       <c r="C14">
-        <f t="shared" ca="1" si="1"/>
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="D14">
-        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="E14">
+        <v>-3</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14">
         <v>17</v>
       </c>
-      <c r="E14">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
-      </c>
       <c r="H14" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I14">
-        <f t="shared" ca="1" si="6"/>
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -2453,30 +2568,37 @@
       <c r="AN14" t="s">
         <v>61</v>
       </c>
+      <c r="AO14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>71</v>
       </c>
       <c r="B15">
-        <f t="shared" ca="1" si="0"/>
-        <v>661</v>
+        <v>976</v>
       </c>
       <c r="C15">
-        <f t="shared" ca="1" si="1"/>
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="D15">
-        <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F15">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -2485,8 +2607,7 @@
         <v>61</v>
       </c>
       <c r="I15">
-        <f t="shared" ca="1" si="6"/>
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -2581,38 +2702,43 @@
       <c r="AN15" t="s">
         <v>61</v>
       </c>
+      <c r="AO15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>72</v>
       </c>
       <c r="B16">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>343</v>
       </c>
       <c r="C16">
-        <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="F16">
-        <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H16" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>61</v>
@@ -2710,39 +2836,44 @@
       <c r="AN16" t="s">
         <v>61</v>
       </c>
+      <c r="AO16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>73</v>
       </c>
       <c r="B17">
-        <f t="shared" ca="1" si="0"/>
-        <v>139</v>
+        <v>364</v>
       </c>
       <c r="C17">
-        <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D17">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17" t="b">
         <v>0</v>
       </c>
-      <c r="F17">
-        <f t="shared" ca="1" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="G17">
-        <f t="shared" ca="1" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="H17" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
-      </c>
       <c r="I17" t="s">
         <v>61</v>
       </c>
@@ -2839,37 +2970,42 @@
       <c r="AN17" t="s">
         <v>61</v>
       </c>
+      <c r="AO17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>74</v>
       </c>
       <c r="B18">
-        <f t="shared" ca="1" si="0"/>
-        <v>185</v>
+        <v>383</v>
       </c>
       <c r="C18">
-        <f t="shared" ca="1" si="1"/>
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="D18">
-        <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <f t="shared" ca="1" si="3"/>
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H18" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I18" t="s">
@@ -2968,38 +3104,43 @@
       <c r="AN18" t="s">
         <v>61</v>
       </c>
+      <c r="AO18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>75</v>
       </c>
       <c r="B19">
-        <f t="shared" ca="1" si="0"/>
-        <v>342</v>
+        <v>447</v>
       </c>
       <c r="C19">
-        <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="D19">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F19">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H19" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -3097,38 +3238,43 @@
       <c r="AN19" t="s">
         <v>61</v>
       </c>
+      <c r="AO19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>76</v>
       </c>
       <c r="B20">
-        <f t="shared" ca="1" si="0"/>
-        <v>371</v>
+        <v>928</v>
       </c>
       <c r="C20">
-        <f t="shared" ca="1" si="1"/>
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="D20">
-        <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <f t="shared" ca="1" si="3"/>
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H20" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
         <v>61</v>
@@ -3226,37 +3372,42 @@
       <c r="AN20" t="s">
         <v>61</v>
       </c>
+      <c r="AO20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>77</v>
       </c>
       <c r="B21">
-        <f t="shared" ca="1" si="0"/>
-        <v>176</v>
+        <v>790</v>
       </c>
       <c r="C21">
-        <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="D21">
-        <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="F21">
-        <f t="shared" ca="1" si="4"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H21" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I21" t="s">
@@ -3355,38 +3506,43 @@
       <c r="AN21" t="s">
         <v>61</v>
       </c>
+      <c r="AO21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>78</v>
       </c>
       <c r="B22">
-        <f t="shared" ca="1" si="0"/>
-        <v>559</v>
+        <v>875</v>
       </c>
       <c r="C22">
-        <f t="shared" ca="1" si="1"/>
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E22">
-        <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <f t="shared" ca="1" si="4"/>
         <v>7</v>
       </c>
       <c r="H22" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
         <v>61</v>
@@ -3484,37 +3640,42 @@
       <c r="AN22" t="s">
         <v>61</v>
       </c>
+      <c r="AO22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>79</v>
       </c>
       <c r="B23">
-        <f t="shared" ca="1" si="0"/>
-        <v>172</v>
+        <v>890</v>
       </c>
       <c r="C23">
-        <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D23">
-        <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <f t="shared" ca="1" si="3"/>
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H23" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>0</v>
       </c>
       <c r="I23" t="s">
@@ -3613,37 +3774,42 @@
       <c r="AN23" t="s">
         <v>61</v>
       </c>
+      <c r="AO23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>80</v>
       </c>
       <c r="B24">
-        <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>401</v>
       </c>
       <c r="C24">
-        <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="D24">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="F24">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H24" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I24" t="s">
@@ -3742,37 +3908,42 @@
       <c r="AN24" t="s">
         <v>61</v>
       </c>
+      <c r="AO24">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>81</v>
       </c>
       <c r="B25">
-        <f t="shared" ca="1" si="0"/>
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="C25">
-        <f t="shared" ca="1" si="1"/>
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="D25">
-        <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E25">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25">
-        <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25">
-        <f t="shared" ca="1" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H25" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I25" t="s">
@@ -3871,37 +4042,42 @@
       <c r="AN25" t="s">
         <v>61</v>
       </c>
+      <c r="AO25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>82</v>
       </c>
       <c r="B26">
-        <f t="shared" ca="1" si="0"/>
-        <v>943</v>
+        <v>626</v>
       </c>
       <c r="C26">
-        <f t="shared" ca="1" si="1"/>
-        <v>184</v>
+        <v>62</v>
       </c>
       <c r="D26">
-        <f t="shared" ca="1" si="2"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E26">
-        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>4</v>
       </c>
-      <c r="F26">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
-      </c>
       <c r="G26">
-        <f t="shared" ca="1" si="4"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H26" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I26" t="s">
@@ -4000,37 +4176,42 @@
       <c r="AN26" t="s">
         <v>61</v>
       </c>
+      <c r="AO26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>83</v>
       </c>
       <c r="B27">
-        <f t="shared" ca="1" si="0"/>
-        <v>803</v>
+        <v>613</v>
       </c>
       <c r="C27">
-        <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="D27">
-        <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H27" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I27" t="s">
@@ -4129,37 +4310,42 @@
       <c r="AN27" t="s">
         <v>61</v>
       </c>
+      <c r="AO27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>84</v>
       </c>
       <c r="B28">
-        <f t="shared" ca="1" si="0"/>
-        <v>895</v>
+        <v>299</v>
       </c>
       <c r="C28">
-        <f t="shared" ca="1" si="1"/>
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="D28">
-        <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <f t="shared" ca="1" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="G28">
         <v>4</v>
       </c>
-      <c r="G28">
-        <f t="shared" ca="1" si="4"/>
-        <v>6</v>
-      </c>
       <c r="H28" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I28" t="s">
@@ -4258,38 +4444,43 @@
       <c r="AN28" t="s">
         <v>61</v>
       </c>
+      <c r="AO28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>85</v>
       </c>
       <c r="B29">
-        <f t="shared" ca="1" si="0"/>
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="C29">
-        <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D29">
-        <f t="shared" ca="1" si="2"/>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E29">
-        <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <f t="shared" ca="1" si="4"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H29" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
         <v>61</v>
@@ -4387,38 +4578,43 @@
       <c r="AN29">
         <v>25</v>
       </c>
+      <c r="AO29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ29">
+        <v>20</v>
+      </c>
+      <c r="AR29" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>86</v>
       </c>
       <c r="B30">
-        <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>670</v>
       </c>
       <c r="C30">
-        <f t="shared" ca="1" si="1"/>
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="D30">
-        <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E30">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="F30">
-        <f t="shared" ca="1" si="4"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="s">
         <v>61</v>
@@ -4516,38 +4712,43 @@
       <c r="AN30" t="s">
         <v>61</v>
       </c>
+      <c r="AO30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>87</v>
       </c>
       <c r="B31">
-        <f t="shared" ca="1" si="0"/>
-        <v>505</v>
+        <v>239</v>
       </c>
       <c r="C31">
-        <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="D31">
-        <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E31">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="F31">
-        <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <f t="shared" ca="1" si="4"/>
         <v>2</v>
       </c>
       <c r="H31" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -4645,37 +4846,42 @@
       <c r="AN31" t="s">
         <v>61</v>
       </c>
+      <c r="AO31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>88</v>
       </c>
       <c r="B32">
-        <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="C32">
-        <f t="shared" ca="1" si="1"/>
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="D32">
-        <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="F32">
-        <f t="shared" ca="1" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H32" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I32" t="s">
@@ -4774,37 +4980,42 @@
       <c r="AN32" t="s">
         <v>61</v>
       </c>
+      <c r="AO32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>89</v>
       </c>
       <c r="B33">
-        <f t="shared" ca="1" si="0"/>
-        <v>457</v>
+        <v>558</v>
       </c>
       <c r="C33">
-        <f t="shared" ca="1" si="1"/>
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="D33">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E33">
-        <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="F33">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H33" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I33" t="s">
@@ -4903,37 +5114,42 @@
       <c r="AN33" t="s">
         <v>61</v>
       </c>
+      <c r="AO33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>90</v>
       </c>
       <c r="B34">
-        <f t="shared" ca="1" si="0"/>
-        <v>712</v>
+        <v>995</v>
       </c>
       <c r="C34">
-        <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D34">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <f t="shared" ca="1" si="3"/>
-        <v>9</v>
+        <v>-7</v>
       </c>
       <c r="F34">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <f t="shared" ca="1" si="4"/>
         <v>18</v>
       </c>
       <c r="H34" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I34" t="s">
@@ -5032,38 +5248,43 @@
       <c r="AN34" t="s">
         <v>61</v>
       </c>
+      <c r="AO34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>91</v>
       </c>
       <c r="B35">
-        <f t="shared" ca="1" si="0"/>
-        <v>421</v>
+        <v>522</v>
       </c>
       <c r="C35">
-        <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D35">
-        <f t="shared" ca="1" si="2"/>
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G35">
-        <f t="shared" ca="1" si="4"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H35" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
         <v>61</v>
@@ -5161,38 +5382,43 @@
       <c r="AN35" t="s">
         <v>61</v>
       </c>
+      <c r="AO35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>92</v>
       </c>
       <c r="B36">
-        <f t="shared" ca="1" si="0"/>
-        <v>660</v>
+        <v>599</v>
       </c>
       <c r="C36">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="D36">
-        <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <f t="shared" ca="1" si="4"/>
         <v>7</v>
       </c>
       <c r="G36">
-        <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H36" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
         <v>61</v>
@@ -5290,37 +5516,42 @@
       <c r="AN36" t="s">
         <v>61</v>
       </c>
+      <c r="AO36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>93</v>
       </c>
       <c r="B37">
-        <f t="shared" ca="1" si="0"/>
-        <v>678</v>
+        <v>795</v>
       </c>
       <c r="C37">
-        <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="D37">
-        <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E37">
-        <f t="shared" ca="1" si="3"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F37">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I37" t="s">
@@ -5419,37 +5650,42 @@
       <c r="AN37" t="s">
         <v>61</v>
       </c>
+      <c r="AO37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="38" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>94</v>
       </c>
       <c r="B38">
-        <f t="shared" ca="1" si="0"/>
-        <v>451</v>
+        <v>624</v>
       </c>
       <c r="C38">
-        <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <f t="shared" ca="1" si="3"/>
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="F38">
-        <f t="shared" ca="1" si="4"/>
         <v>7</v>
       </c>
       <c r="G38">
-        <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H38" t="b">
-        <f t="shared" ca="1" si="5"/>
         <v>1</v>
       </c>
       <c r="I38" t="s">
@@ -5548,38 +5784,43 @@
       <c r="AN38" t="s">
         <v>61</v>
       </c>
+      <c r="AO38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="39" spans="1:40" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>95</v>
       </c>
       <c r="B39">
-        <f t="shared" ca="1" si="0"/>
-        <v>253</v>
+        <v>647</v>
       </c>
       <c r="C39">
-        <f t="shared" ca="1" si="1"/>
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39">
-        <f t="shared" ca="1" si="3"/>
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="F39">
-        <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G39">
-        <f ca="1">RANDBETWEEN(0,20)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H39" t="b">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="s">
         <v>61</v>
@@ -5675,6 +5916,18 @@
         <v>61</v>
       </c>
       <c r="AN39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR39" t="s">
         <v>61</v>
       </c>
     </row>

--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9749B5D6-F3CB-4819-A3EA-E6F2D20CF4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF69EFD-376C-45F3-9291-445E25CA3565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="106">
   <si>
     <t>Profile--&gt;</t>
   </si>
@@ -339,6 +339,21 @@
   </si>
   <si>
     <t>HeatConsumed</t>
+  </si>
+  <si>
+    <t>FuelType</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>JP-5</t>
+  </si>
+  <si>
+    <t>Marine Diesel Oil</t>
+  </si>
+  <si>
+    <t>Heavy Fuel Oil</t>
   </si>
 </sst>
 </file>
@@ -656,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR39"/>
+  <dimension ref="A1:AS39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="29.7890625" customWidth="1"/>
@@ -670,42 +685,42 @@
     <col min="9" max="9" width="19.7890625" customWidth="1"/>
     <col min="10" max="10" width="14.62890625" customWidth="1"/>
     <col min="11" max="11" width="15.41796875" customWidth="1"/>
-    <col min="12" max="12" width="18.20703125" customWidth="1"/>
-    <col min="13" max="13" width="15.41796875" customWidth="1"/>
-    <col min="14" max="14" width="19.7890625" customWidth="1"/>
-    <col min="15" max="15" width="14.89453125" customWidth="1"/>
-    <col min="16" max="16" width="13.734375" customWidth="1"/>
-    <col min="17" max="17" width="15.3125" customWidth="1"/>
-    <col min="18" max="18" width="13.83984375" customWidth="1"/>
-    <col min="19" max="19" width="16.20703125" customWidth="1"/>
-    <col min="20" max="20" width="13.83984375" customWidth="1"/>
-    <col min="21" max="21" width="14.20703125" customWidth="1"/>
-    <col min="22" max="22" width="14.5234375" customWidth="1"/>
-    <col min="23" max="23" width="13.734375" customWidth="1"/>
-    <col min="24" max="24" width="13.05078125" customWidth="1"/>
-    <col min="25" max="25" width="13.578125" customWidth="1"/>
-    <col min="26" max="26" width="15.05078125" customWidth="1"/>
-    <col min="27" max="27" width="15.578125" customWidth="1"/>
-    <col min="28" max="28" width="13.47265625" customWidth="1"/>
-    <col min="29" max="29" width="11.89453125" customWidth="1"/>
-    <col min="30" max="30" width="14.5234375" customWidth="1"/>
-    <col min="31" max="31" width="13.20703125" customWidth="1"/>
-    <col min="32" max="32" width="13.47265625" customWidth="1"/>
-    <col min="33" max="33" width="13.83984375" customWidth="1"/>
-    <col min="34" max="34" width="14.1015625" customWidth="1"/>
-    <col min="35" max="35" width="14.5234375" customWidth="1"/>
-    <col min="36" max="36" width="14.3671875" customWidth="1"/>
-    <col min="37" max="37" width="14.26171875" customWidth="1"/>
-    <col min="38" max="38" width="13.05078125" customWidth="1"/>
-    <col min="39" max="39" width="14.26171875" customWidth="1"/>
-    <col min="40" max="40" width="12.9453125" customWidth="1"/>
-    <col min="41" max="41" width="13.05078125" customWidth="1"/>
-    <col min="42" max="42" width="15.9453125" customWidth="1"/>
-    <col min="43" max="43" width="16.62890625" customWidth="1"/>
-    <col min="44" max="44" width="12.7890625" customWidth="1"/>
+    <col min="12" max="13" width="18.20703125" customWidth="1"/>
+    <col min="14" max="14" width="15.41796875" customWidth="1"/>
+    <col min="15" max="15" width="19.7890625" customWidth="1"/>
+    <col min="16" max="16" width="14.89453125" customWidth="1"/>
+    <col min="17" max="17" width="13.734375" customWidth="1"/>
+    <col min="18" max="18" width="15.3125" customWidth="1"/>
+    <col min="19" max="19" width="13.83984375" customWidth="1"/>
+    <col min="20" max="20" width="16.20703125" customWidth="1"/>
+    <col min="21" max="21" width="13.83984375" customWidth="1"/>
+    <col min="22" max="22" width="14.20703125" customWidth="1"/>
+    <col min="23" max="23" width="14.5234375" customWidth="1"/>
+    <col min="24" max="24" width="13.734375" customWidth="1"/>
+    <col min="25" max="25" width="13.05078125" customWidth="1"/>
+    <col min="26" max="26" width="13.578125" customWidth="1"/>
+    <col min="27" max="27" width="15.05078125" customWidth="1"/>
+    <col min="28" max="28" width="15.578125" customWidth="1"/>
+    <col min="29" max="29" width="13.47265625" customWidth="1"/>
+    <col min="30" max="30" width="11.89453125" customWidth="1"/>
+    <col min="31" max="31" width="14.5234375" customWidth="1"/>
+    <col min="32" max="32" width="13.20703125" customWidth="1"/>
+    <col min="33" max="33" width="13.47265625" customWidth="1"/>
+    <col min="34" max="34" width="13.83984375" customWidth="1"/>
+    <col min="35" max="35" width="14.1015625" customWidth="1"/>
+    <col min="36" max="36" width="14.5234375" customWidth="1"/>
+    <col min="37" max="37" width="14.3671875" customWidth="1"/>
+    <col min="38" max="38" width="14.26171875" customWidth="1"/>
+    <col min="39" max="39" width="13.05078125" customWidth="1"/>
+    <col min="40" max="40" width="14.26171875" customWidth="1"/>
+    <col min="41" max="41" width="12.9453125" customWidth="1"/>
+    <col min="42" max="42" width="13.05078125" customWidth="1"/>
+    <col min="43" max="43" width="15.9453125" customWidth="1"/>
+    <col min="44" max="44" width="16.62890625" customWidth="1"/>
+    <col min="45" max="45" width="12.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -752,7 +767,7 @@
         <v>3</v>
       </c>
       <c r="P1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q1" t="s">
         <v>4</v>
@@ -764,7 +779,7 @@
         <v>4</v>
       </c>
       <c r="T1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U1" t="s">
         <v>5</v>
@@ -776,7 +791,7 @@
         <v>5</v>
       </c>
       <c r="X1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y1" t="s">
         <v>6</v>
@@ -788,7 +803,7 @@
         <v>6</v>
       </c>
       <c r="AB1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC1" t="s">
         <v>7</v>
@@ -827,7 +842,7 @@
         <v>7</v>
       </c>
       <c r="AO1" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="AP1" t="s">
         <v>96</v>
@@ -838,8 +853,11 @@
       <c r="AR1" t="s">
         <v>96</v>
       </c>
+      <c r="AS1" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -877,7 +895,7 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N2" t="s">
         <v>13</v>
@@ -886,67 +904,67 @@
         <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="s">
         <v>14</v>
       </c>
       <c r="R2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S2" t="s">
         <v>15</v>
       </c>
       <c r="T2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U2" t="s">
         <v>16</v>
       </c>
       <c r="V2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W2" t="s">
         <v>17</v>
       </c>
       <c r="X2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="s">
         <v>18</v>
       </c>
       <c r="Z2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
       <c r="AB2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="s">
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="s">
         <v>21</v>
       </c>
       <c r="AF2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="s">
         <v>22</v>
       </c>
       <c r="AH2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="s">
         <v>23</v>
       </c>
       <c r="AJ2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="s">
         <v>24</v>
@@ -961,19 +979,22 @@
         <v>24</v>
       </c>
       <c r="AO2" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="s">
         <v>97</v>
       </c>
       <c r="AQ2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AR2" t="s">
         <v>98</v>
       </c>
+      <c r="AS2" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1011,103 +1032,106 @@
         <v>32</v>
       </c>
       <c r="M3" t="s">
+        <v>101</v>
+      </c>
+      <c r="N3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>36</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>32</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>38</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>39</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>40</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>32</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>32</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>42</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>32</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>44</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>32</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>45</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>32</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>46</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>32</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>47</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>32</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>48</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>49</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AO3" t="s">
         <v>50</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AP3" t="s">
         <v>100</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AQ3" t="s">
         <v>32</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AR3" t="s">
         <v>99</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -1145,82 +1169,82 @@
         <v>56</v>
       </c>
       <c r="M4" t="s">
+        <v>102</v>
+      </c>
+      <c r="N4" t="s">
         <v>57</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>58</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>56</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>59</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>56</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>59</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>56</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>57</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>56</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>57</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>56</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>57</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>56</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>57</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>56</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>57</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>56</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>57</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>56</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
         <v>57</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>56</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>57</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>56</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>57</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>56</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>57</v>
       </c>
       <c r="AM4" t="s">
         <v>57</v>
@@ -1229,19 +1253,22 @@
         <v>57</v>
       </c>
       <c r="AO4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP4" t="s">
         <v>59</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>56</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>59</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1374,8 +1401,11 @@
       <c r="AR5" t="s">
         <v>61</v>
       </c>
+      <c r="AS5" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1508,8 +1538,11 @@
       <c r="AR6" t="s">
         <v>61</v>
       </c>
+      <c r="AS6" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -1642,8 +1675,11 @@
       <c r="AR7" t="s">
         <v>61</v>
       </c>
+      <c r="AS7" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>64</v>
       </c>
@@ -1675,13 +1711,13 @@
         <v>1</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="N8" t="s">
         <v>61</v>
@@ -1689,50 +1725,50 @@
       <c r="O8" t="s">
         <v>61</v>
       </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="s">
-        <v>61</v>
+      <c r="P8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
       </c>
       <c r="S8" t="s">
         <v>61</v>
       </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" t="s">
-        <v>61</v>
+      <c r="T8" t="s">
+        <v>61</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
       </c>
       <c r="W8" t="s">
         <v>61</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>61</v>
+      <c r="X8" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
       </c>
       <c r="AA8" t="s">
         <v>61</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC8">
         <v>12</v>
       </c>
-      <c r="AC8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>61</v>
+      <c r="AD8" t="b">
+        <v>1</v>
       </c>
       <c r="AE8" t="s">
         <v>61</v>
@@ -1776,8 +1812,11 @@
       <c r="AR8" t="s">
         <v>61</v>
       </c>
+      <c r="AS8" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -1823,38 +1862,38 @@
       <c r="O9" t="s">
         <v>61</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="s">
-        <v>61</v>
+      <c r="P9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>61</v>
       </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" t="s">
-        <v>61</v>
+      <c r="T9" t="s">
+        <v>61</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
       </c>
       <c r="W9" t="s">
         <v>61</v>
       </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>61</v>
+      <c r="X9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
       </c>
       <c r="AA9" t="s">
         <v>61</v>
@@ -1910,8 +1949,11 @@
       <c r="AR9" t="s">
         <v>61</v>
       </c>
+      <c r="AS9" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>66</v>
       </c>
@@ -1969,26 +2011,26 @@
       <c r="S10" t="s">
         <v>61</v>
       </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" t="s">
-        <v>61</v>
+      <c r="T10" t="s">
+        <v>61</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
       </c>
       <c r="W10" t="s">
         <v>61</v>
       </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>61</v>
+      <c r="X10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
       </c>
       <c r="AA10" t="s">
         <v>61</v>
@@ -2044,8 +2086,11 @@
       <c r="AR10" t="s">
         <v>61</v>
       </c>
+      <c r="AS10" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -2103,14 +2148,14 @@
       <c r="S11" t="s">
         <v>61</v>
       </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="s">
-        <v>61</v>
+      <c r="T11" t="s">
+        <v>61</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
       </c>
       <c r="W11" t="s">
         <v>61</v>
@@ -2178,8 +2223,11 @@
       <c r="AR11" t="s">
         <v>61</v>
       </c>
+      <c r="AS11" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -2211,13 +2259,13 @@
         <v>1</v>
       </c>
       <c r="K12">
-        <v>15</v>
+        <v>2.5000000000000001E-4</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
         <v>61</v>
@@ -2237,38 +2285,38 @@
       <c r="S12" t="s">
         <v>61</v>
       </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12" t="b">
-        <v>1</v>
-      </c>
-      <c r="V12" t="s">
-        <v>61</v>
+      <c r="T12" t="s">
+        <v>61</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
       </c>
       <c r="W12" t="s">
         <v>61</v>
       </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>61</v>
+      <c r="X12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
       </c>
       <c r="AA12" t="s">
         <v>61</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC12">
         <v>6</v>
       </c>
-      <c r="AC12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>61</v>
+      <c r="AD12" t="b">
+        <v>1</v>
       </c>
       <c r="AE12" t="s">
         <v>61</v>
@@ -2312,8 +2360,11 @@
       <c r="AR12" t="s">
         <v>61</v>
       </c>
+      <c r="AS12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>69</v>
       </c>
@@ -2446,8 +2497,11 @@
       <c r="AR13" t="s">
         <v>61</v>
       </c>
+      <c r="AS13" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -2580,8 +2634,11 @@
       <c r="AR14" t="s">
         <v>61</v>
       </c>
+      <c r="AS14" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -2714,8 +2771,11 @@
       <c r="AR15" t="s">
         <v>61</v>
       </c>
+      <c r="AS15" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -2785,14 +2845,14 @@
       <c r="W16" t="s">
         <v>61</v>
       </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>61</v>
+      <c r="X16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
       </c>
       <c r="AA16" t="s">
         <v>61</v>
@@ -2848,8 +2908,11 @@
       <c r="AR16" t="s">
         <v>61</v>
       </c>
+      <c r="AS16" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -2982,8 +3045,11 @@
       <c r="AR17" t="s">
         <v>61</v>
       </c>
+      <c r="AS17" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -3029,14 +3095,14 @@
       <c r="O18" t="s">
         <v>61</v>
       </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="s">
-        <v>61</v>
+      <c r="P18" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
       </c>
       <c r="S18" t="s">
         <v>61</v>
@@ -3116,8 +3182,11 @@
       <c r="AR18" t="s">
         <v>61</v>
       </c>
+      <c r="AS18" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -3163,26 +3232,26 @@
       <c r="O19" t="s">
         <v>61</v>
       </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="s">
-        <v>61</v>
+      <c r="P19" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
       </c>
       <c r="S19" t="s">
         <v>61</v>
       </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19" t="b">
-        <v>1</v>
-      </c>
-      <c r="V19" t="s">
-        <v>61</v>
+      <c r="T19" t="s">
+        <v>61</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
       </c>
       <c r="W19" t="s">
         <v>61</v>
@@ -3250,8 +3319,11 @@
       <c r="AR19" t="s">
         <v>61</v>
       </c>
+      <c r="AS19" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -3297,14 +3369,14 @@
       <c r="O20" t="s">
         <v>61</v>
       </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="s">
-        <v>61</v>
+      <c r="P20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
       </c>
       <c r="S20" t="s">
         <v>61</v>
@@ -3384,8 +3456,11 @@
       <c r="AR20" t="s">
         <v>61</v>
       </c>
+      <c r="AS20" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -3518,8 +3593,11 @@
       <c r="AR21" t="s">
         <v>61</v>
       </c>
+      <c r="AS21" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>78</v>
       </c>
@@ -3571,20 +3649,20 @@
       <c r="Q22" t="s">
         <v>61</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="s">
+        <v>61</v>
+      </c>
+      <c r="S22">
         <v>100</v>
       </c>
-      <c r="S22" t="b">
-        <v>1</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22" t="b">
-        <v>1</v>
-      </c>
-      <c r="V22" t="s">
-        <v>61</v>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
       </c>
       <c r="W22" t="s">
         <v>61</v>
@@ -3652,8 +3730,11 @@
       <c r="AR22" t="s">
         <v>61</v>
       </c>
+      <c r="AS22" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -3699,14 +3780,14 @@
       <c r="O23" t="s">
         <v>61</v>
       </c>
-      <c r="P23">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="s">
-        <v>61</v>
+      <c r="P23" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
       </c>
       <c r="S23" t="s">
         <v>61</v>
@@ -3753,14 +3834,14 @@
       <c r="AG23" t="s">
         <v>61</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI23">
         <v>8</v>
       </c>
-      <c r="AI23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>61</v>
+      <c r="AJ23" t="b">
+        <v>1</v>
       </c>
       <c r="AK23" t="s">
         <v>61</v>
@@ -3786,8 +3867,11 @@
       <c r="AR23" t="s">
         <v>61</v>
       </c>
+      <c r="AS23" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>80</v>
       </c>
@@ -3824,35 +3908,35 @@
       <c r="L24" t="s">
         <v>61</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24">
         <v>100</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>10000</v>
       </c>
-      <c r="O24" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="s">
-        <v>61</v>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
       </c>
       <c r="S24" t="s">
         <v>61</v>
       </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24" t="b">
-        <v>1</v>
-      </c>
-      <c r="V24" t="s">
-        <v>61</v>
+      <c r="T24" t="s">
+        <v>61</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
       </c>
       <c r="W24" t="s">
         <v>61</v>
@@ -3887,14 +3971,14 @@
       <c r="AG24" t="s">
         <v>61</v>
       </c>
-      <c r="AH24">
+      <c r="AH24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI24">
         <v>11</v>
       </c>
-      <c r="AI24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>61</v>
+      <c r="AJ24" t="b">
+        <v>1</v>
       </c>
       <c r="AK24" t="s">
         <v>61</v>
@@ -3908,20 +3992,23 @@
       <c r="AN24" t="s">
         <v>61</v>
       </c>
-      <c r="AO24">
-        <v>1</v>
-      </c>
-      <c r="AP24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>61</v>
+      <c r="AO24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP24">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="b">
+        <v>1</v>
       </c>
       <c r="AR24" t="s">
         <v>61</v>
       </c>
+      <c r="AS24" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>81</v>
       </c>
@@ -3967,26 +4054,26 @@
       <c r="O25" t="s">
         <v>61</v>
       </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="s">
-        <v>61</v>
+      <c r="P25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
       </c>
       <c r="S25" t="s">
         <v>61</v>
       </c>
-      <c r="T25">
-        <v>1</v>
-      </c>
-      <c r="U25" t="b">
-        <v>1</v>
-      </c>
-      <c r="V25" t="s">
-        <v>61</v>
+      <c r="T25" t="s">
+        <v>61</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
       </c>
       <c r="W25" t="s">
         <v>61</v>
@@ -3997,14 +4084,14 @@
       <c r="Y25" t="s">
         <v>61</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA25">
         <v>55</v>
       </c>
-      <c r="AA25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>61</v>
+      <c r="AB25" t="b">
+        <v>1</v>
       </c>
       <c r="AC25" t="s">
         <v>61</v>
@@ -4054,8 +4141,11 @@
       <c r="AR25" t="s">
         <v>61</v>
       </c>
+      <c r="AS25" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -4101,38 +4191,38 @@
       <c r="O26" t="s">
         <v>61</v>
       </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="s">
-        <v>61</v>
+      <c r="P26" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
       </c>
       <c r="S26" t="s">
         <v>61</v>
       </c>
-      <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26" t="b">
-        <v>1</v>
-      </c>
-      <c r="V26" t="s">
-        <v>61</v>
+      <c r="T26" t="s">
+        <v>61</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
       </c>
       <c r="W26" t="s">
         <v>61</v>
       </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>61</v>
+      <c r="X26" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
       </c>
       <c r="AA26" t="s">
         <v>61</v>
@@ -4188,8 +4278,11 @@
       <c r="AR26" t="s">
         <v>61</v>
       </c>
+      <c r="AS26" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>83</v>
       </c>
@@ -4221,13 +4314,13 @@
         <v>61</v>
       </c>
       <c r="K27">
-        <v>12</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
       </c>
       <c r="M27" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="N27" t="s">
         <v>61</v>
@@ -4235,38 +4328,38 @@
       <c r="O27" t="s">
         <v>61</v>
       </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="s">
-        <v>61</v>
+      <c r="P27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
       </c>
       <c r="S27" t="s">
         <v>61</v>
       </c>
-      <c r="T27">
-        <v>1</v>
-      </c>
-      <c r="U27" t="b">
-        <v>1</v>
-      </c>
-      <c r="V27" t="s">
-        <v>61</v>
+      <c r="T27" t="s">
+        <v>61</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
       </c>
       <c r="W27" t="s">
         <v>61</v>
       </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>61</v>
+      <c r="X27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
       </c>
       <c r="AA27" t="s">
         <v>61</v>
@@ -4283,14 +4376,14 @@
       <c r="AE27" t="s">
         <v>61</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG27">
         <v>6</v>
       </c>
-      <c r="AG27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>61</v>
+      <c r="AH27" t="b">
+        <v>1</v>
       </c>
       <c r="AI27" t="s">
         <v>61</v>
@@ -4322,8 +4415,11 @@
       <c r="AR27" t="s">
         <v>61</v>
       </c>
+      <c r="AS27" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -4387,14 +4483,14 @@
       <c r="U28" t="s">
         <v>61</v>
       </c>
-      <c r="V28">
+      <c r="V28" t="s">
+        <v>61</v>
+      </c>
+      <c r="W28">
         <v>50</v>
       </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-      <c r="X28" t="s">
-        <v>61</v>
+      <c r="X28" t="b">
+        <v>1</v>
       </c>
       <c r="Y28" t="s">
         <v>61</v>
@@ -4456,8 +4552,11 @@
       <c r="AR28" t="s">
         <v>61</v>
       </c>
+      <c r="AS28" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -4503,38 +4602,38 @@
       <c r="O29" t="s">
         <v>61</v>
       </c>
-      <c r="P29">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="s">
-        <v>61</v>
+      <c r="P29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
       </c>
       <c r="S29" t="s">
         <v>61</v>
       </c>
-      <c r="T29">
-        <v>1</v>
-      </c>
-      <c r="U29" t="b">
-        <v>1</v>
-      </c>
-      <c r="V29" t="s">
-        <v>61</v>
+      <c r="T29" t="s">
+        <v>61</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
       </c>
       <c r="W29" t="s">
         <v>61</v>
       </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>61</v>
+      <c r="X29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y29">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
       </c>
       <c r="AA29" t="s">
         <v>61</v>
@@ -4563,14 +4662,14 @@
       <c r="AI29" t="s">
         <v>61</v>
       </c>
-      <c r="AJ29">
+      <c r="AJ29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK29">
         <v>25</v>
       </c>
-      <c r="AK29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL29">
-        <v>25</v>
+      <c r="AL29" t="b">
+        <v>1</v>
       </c>
       <c r="AM29">
         <v>25</v>
@@ -4578,20 +4677,23 @@
       <c r="AN29">
         <v>25</v>
       </c>
-      <c r="AO29" t="s">
-        <v>61</v>
+      <c r="AO29">
+        <v>25</v>
       </c>
       <c r="AP29" t="s">
         <v>61</v>
       </c>
-      <c r="AQ29">
+      <c r="AQ29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR29">
         <v>20</v>
       </c>
-      <c r="AR29" t="b">
+      <c r="AS29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -4637,26 +4739,26 @@
       <c r="O30" t="s">
         <v>61</v>
       </c>
-      <c r="P30">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="s">
-        <v>61</v>
+      <c r="P30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
       </c>
       <c r="S30" t="s">
         <v>61</v>
       </c>
-      <c r="T30">
-        <v>1</v>
-      </c>
-      <c r="U30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V30" t="s">
-        <v>61</v>
+      <c r="T30" t="s">
+        <v>61</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
       </c>
       <c r="W30" t="s">
         <v>61</v>
@@ -4724,8 +4826,11 @@
       <c r="AR30" t="s">
         <v>61</v>
       </c>
+      <c r="AS30" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -4771,38 +4876,38 @@
       <c r="O31" t="s">
         <v>61</v>
       </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="s">
-        <v>61</v>
+      <c r="P31" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
       </c>
       <c r="S31" t="s">
         <v>61</v>
       </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31" t="b">
-        <v>1</v>
-      </c>
-      <c r="V31" t="s">
-        <v>61</v>
+      <c r="T31" t="s">
+        <v>61</v>
+      </c>
+      <c r="U31">
+        <v>1</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
       </c>
       <c r="W31" t="s">
         <v>61</v>
       </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>61</v>
+      <c r="X31" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y31">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
       </c>
       <c r="AA31" t="s">
         <v>61</v>
@@ -4819,14 +4924,14 @@
       <c r="AE31" t="s">
         <v>61</v>
       </c>
-      <c r="AF31">
+      <c r="AF31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG31">
         <v>8</v>
       </c>
-      <c r="AG31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>61</v>
+      <c r="AH31" t="b">
+        <v>1</v>
       </c>
       <c r="AI31" t="s">
         <v>61</v>
@@ -4858,8 +4963,11 @@
       <c r="AR31" t="s">
         <v>61</v>
       </c>
+      <c r="AS31" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>88</v>
       </c>
@@ -4905,14 +5013,14 @@
       <c r="O32" t="s">
         <v>61</v>
       </c>
-      <c r="P32">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
-      </c>
-      <c r="R32" t="s">
-        <v>61</v>
+      <c r="P32" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
       </c>
       <c r="S32" t="s">
         <v>61</v>
@@ -4947,20 +5055,20 @@
       <c r="AC32" t="s">
         <v>61</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE32">
         <v>9</v>
       </c>
-      <c r="AE32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF32">
+      <c r="AF32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32">
         <v>9</v>
       </c>
-      <c r="AG32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>61</v>
+      <c r="AH32" t="b">
+        <v>1</v>
       </c>
       <c r="AI32" t="s">
         <v>61</v>
@@ -4992,8 +5100,11 @@
       <c r="AR32" t="s">
         <v>61</v>
       </c>
+      <c r="AS32" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -5039,14 +5150,14 @@
       <c r="O33" t="s">
         <v>61</v>
       </c>
-      <c r="P33">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>1</v>
-      </c>
-      <c r="R33" t="s">
-        <v>61</v>
+      <c r="P33" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
       </c>
       <c r="S33" t="s">
         <v>61</v>
@@ -5081,20 +5192,20 @@
       <c r="AC33" t="s">
         <v>61</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE33">
         <v>7</v>
       </c>
-      <c r="AE33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF33">
+      <c r="AF33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33">
         <v>3</v>
       </c>
-      <c r="AG33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>61</v>
+      <c r="AH33" t="b">
+        <v>1</v>
       </c>
       <c r="AI33" t="s">
         <v>61</v>
@@ -5126,8 +5237,11 @@
       <c r="AR33" t="s">
         <v>61</v>
       </c>
+      <c r="AS33" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -5260,8 +5374,11 @@
       <c r="AR34" t="s">
         <v>61</v>
       </c>
+      <c r="AS34" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>91</v>
       </c>
@@ -5394,8 +5511,11 @@
       <c r="AR35" t="s">
         <v>61</v>
       </c>
+      <c r="AS35" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>92</v>
       </c>
@@ -5441,14 +5561,14 @@
       <c r="O36" t="s">
         <v>61</v>
       </c>
-      <c r="P36">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>1</v>
-      </c>
-      <c r="R36" t="s">
-        <v>61</v>
+      <c r="P36" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
       </c>
       <c r="S36" t="s">
         <v>61</v>
@@ -5528,8 +5648,11 @@
       <c r="AR36" t="s">
         <v>61</v>
       </c>
+      <c r="AS36" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>93</v>
       </c>
@@ -5575,14 +5698,14 @@
       <c r="O37" t="s">
         <v>61</v>
       </c>
-      <c r="P37">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R37" t="s">
-        <v>61</v>
+      <c r="P37" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
       </c>
       <c r="S37" t="s">
         <v>61</v>
@@ -5662,8 +5785,11 @@
       <c r="AR37" t="s">
         <v>61</v>
       </c>
+      <c r="AS37" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -5709,14 +5835,14 @@
       <c r="O38" t="s">
         <v>61</v>
       </c>
-      <c r="P38">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" t="s">
-        <v>61</v>
+      <c r="P38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
       </c>
       <c r="S38" t="s">
         <v>61</v>
@@ -5796,8 +5922,11 @@
       <c r="AR38" t="s">
         <v>61</v>
       </c>
+      <c r="AS38" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>95</v>
       </c>
@@ -5843,14 +5972,14 @@
       <c r="O39" t="s">
         <v>61</v>
       </c>
-      <c r="P39">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>1</v>
-      </c>
-      <c r="R39" t="s">
-        <v>61</v>
+      <c r="P39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
       </c>
       <c r="S39" t="s">
         <v>61</v>
@@ -5928,6 +6057,9 @@
         <v>61</v>
       </c>
       <c r="AR39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS39" t="s">
         <v>61</v>
       </c>
     </row>

--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF69EFD-376C-45F3-9291-445E25CA3565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7BD9F7-4D26-4ABA-BC96-72C0BA7B55BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="106">
   <si>
     <t>Profile--&gt;</t>
   </si>
@@ -1704,11 +1704,11 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>151</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
       </c>
       <c r="K8">
         <v>7.0000000000000001E-3</v>

--- a/data/input_tables/Properties.xlsx
+++ b/data/input_tables/Properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kkoch28\Downloads\NAVSEA RESEARCH\data\input_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7BD9F7-4D26-4ABA-BC96-72C0BA7B55BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555890D8-F137-4A3E-915A-296AF5D8C10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="8595" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="117">
   <si>
     <t>Profile--&gt;</t>
   </si>
@@ -230,18 +230,6 @@
     <t>12X (STIFFENERS)</t>
   </si>
   <si>
-    <t>20X (MAIN ENGINE)</t>
-  </si>
-  <si>
-    <t>21X (PROPULSORS)</t>
-  </si>
-  <si>
-    <t>22X (SHAFTING)</t>
-  </si>
-  <si>
-    <t>23X (POWER TRANSMISSION)</t>
-  </si>
-  <si>
     <t>30X (GENERATOR SETS)</t>
   </si>
   <si>
@@ -278,9 +266,6 @@
     <t>51X (LUBE OIL)</t>
   </si>
   <si>
-    <t>52X (FUEL)</t>
-  </si>
-  <si>
     <t>53X (COMPRESSED AIR)</t>
   </si>
   <si>
@@ -354,6 +339,54 @@
   </si>
   <si>
     <t>Heavy Fuel Oil</t>
+  </si>
+  <si>
+    <t>20X DIESEL ENGINE</t>
+  </si>
+  <si>
+    <t>20X ABSENT</t>
+  </si>
+  <si>
+    <t>21X SHAFT DRIVE + MANEUVERING THRUSTER</t>
+  </si>
+  <si>
+    <t>21X ELECTRIC DRIVE + MANEUVERING THRUSTER</t>
+  </si>
+  <si>
+    <t>21X WATER JET + MANEUVERING THRUSTER</t>
+  </si>
+  <si>
+    <t>21X SHAFT DRIVE</t>
+  </si>
+  <si>
+    <t>21X ELECTRIC DRIVE</t>
+  </si>
+  <si>
+    <t>21X WATER JET</t>
+  </si>
+  <si>
+    <t>21X ABSENT</t>
+  </si>
+  <si>
+    <t>22X ABSENT</t>
+  </si>
+  <si>
+    <t>22X MECHANICAL</t>
+  </si>
+  <si>
+    <t>23X ABSENT</t>
+  </si>
+  <si>
+    <t>23X MECHANICAL</t>
+  </si>
+  <si>
+    <t>23X MECHANICAL WITH POWER TAKEOFF</t>
+  </si>
+  <si>
+    <t>52X ABSENT</t>
+  </si>
+  <si>
+    <t>52X FUEL</t>
   </si>
 </sst>
 </file>
@@ -671,10 +704,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS39"/>
+  <dimension ref="A1:AS50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="29.7890625" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
     <col min="2" max="2" width="21.89453125" customWidth="1"/>
     <col min="3" max="3" width="22.9453125" customWidth="1"/>
     <col min="4" max="4" width="22.68359375" customWidth="1"/>
@@ -845,16 +878,16 @@
         <v>7</v>
       </c>
       <c r="AP1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AQ1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AR1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AS1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.55000000000000004">
@@ -982,16 +1015,16 @@
         <v>24</v>
       </c>
       <c r="AP2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="AQ2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="AR2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="AS2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.55000000000000004">
@@ -1032,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N3" t="s">
         <v>35</v>
@@ -1119,13 +1152,13 @@
         <v>50</v>
       </c>
       <c r="AP3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AQ3" t="s">
         <v>32</v>
       </c>
       <c r="AR3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AS3" t="s">
         <v>32</v>
@@ -1169,7 +1202,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s">
         <v>57</v>
@@ -1681,7 +1714,7 @@
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="B8">
         <v>423</v>
@@ -1717,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N8" t="s">
         <v>61</v>
@@ -1818,28 +1851,28 @@
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9">
-        <v>198</v>
-      </c>
-      <c r="C9">
-        <v>167</v>
-      </c>
-      <c r="D9">
-        <v>26</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>18</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
       </c>
       <c r="I9" t="s">
         <v>61</v>
@@ -1865,11 +1898,11 @@
       <c r="P9" t="s">
         <v>61</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9" t="b">
-        <v>1</v>
+      <c r="Q9" t="s">
+        <v>61</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
       </c>
       <c r="S9" t="s">
         <v>61</v>
@@ -1877,11 +1910,11 @@
       <c r="T9" t="s">
         <v>61</v>
       </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9" t="b">
-        <v>1</v>
+      <c r="U9" t="s">
+        <v>61</v>
+      </c>
+      <c r="V9" t="s">
+        <v>61</v>
       </c>
       <c r="W9" t="s">
         <v>61</v>
@@ -1889,11 +1922,11 @@
       <c r="X9" t="s">
         <v>61</v>
       </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>1</v>
+      <c r="Y9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>61</v>
       </c>
       <c r="AA9" t="s">
         <v>61</v>
@@ -1955,28 +1988,28 @@
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="B10">
-        <v>563</v>
+        <v>198</v>
       </c>
       <c r="C10">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" t="s">
-        <v>61</v>
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>18</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
       </c>
       <c r="I10" t="s">
         <v>61</v>
@@ -2002,11 +2035,11 @@
       <c r="P10" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" t="s">
-        <v>61</v>
-      </c>
-      <c r="R10" t="s">
-        <v>61</v>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
       </c>
       <c r="S10" t="s">
         <v>61</v>
@@ -2092,34 +2125,34 @@
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="B11">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="C11">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11">
-        <v>129</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>18</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
       </c>
       <c r="K11" t="s">
         <v>61</v>
@@ -2139,11 +2172,11 @@
       <c r="P11" t="s">
         <v>61</v>
       </c>
-      <c r="Q11" t="s">
-        <v>61</v>
-      </c>
-      <c r="R11" t="s">
-        <v>61</v>
+      <c r="Q11">
+        <v>2</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
       </c>
       <c r="S11" t="s">
         <v>61</v>
@@ -2152,7 +2185,7 @@
         <v>61</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2163,11 +2196,11 @@
       <c r="X11" t="s">
         <v>61</v>
       </c>
-      <c r="Y11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>61</v>
+      <c r="Y11">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
       </c>
       <c r="AA11" t="s">
         <v>61</v>
@@ -2229,43 +2262,43 @@
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="B12">
-        <v>441</v>
+        <v>54</v>
       </c>
       <c r="C12">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12">
-        <v>113</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>18</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="N12" t="s">
         <v>61</v>
@@ -2276,11 +2309,11 @@
       <c r="P12" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" t="s">
-        <v>61</v>
-      </c>
-      <c r="R12" t="s">
-        <v>61</v>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
       </c>
       <c r="S12" t="s">
         <v>61</v>
@@ -2289,7 +2322,7 @@
         <v>61</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -2301,7 +2334,7 @@
         <v>61</v>
       </c>
       <c r="Y12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="b">
         <v>1</v>
@@ -2312,11 +2345,11 @@
       <c r="AB12" t="s">
         <v>61</v>
       </c>
-      <c r="AC12">
-        <v>6</v>
-      </c>
-      <c r="AD12" t="b">
-        <v>1</v>
+      <c r="AC12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>61</v>
       </c>
       <c r="AE12" t="s">
         <v>61</v>
@@ -2366,28 +2399,28 @@
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="B13">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="C13">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F13">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s">
-        <v>61</v>
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>18</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
       </c>
       <c r="I13" t="s">
         <v>61</v>
@@ -2413,11 +2446,11 @@
       <c r="P13" t="s">
         <v>61</v>
       </c>
-      <c r="Q13" t="s">
-        <v>61</v>
-      </c>
-      <c r="R13" t="s">
-        <v>61</v>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
       </c>
       <c r="S13" t="s">
         <v>61</v>
@@ -2425,11 +2458,11 @@
       <c r="T13" t="s">
         <v>61</v>
       </c>
-      <c r="U13" t="s">
-        <v>61</v>
-      </c>
-      <c r="V13" t="s">
-        <v>61</v>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
       </c>
       <c r="W13" t="s">
         <v>61</v>
@@ -2437,11 +2470,11 @@
       <c r="X13" t="s">
         <v>61</v>
       </c>
-      <c r="Y13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>61</v>
+      <c r="Y13">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
       </c>
       <c r="AA13" t="s">
         <v>61</v>
@@ -2503,34 +2536,34 @@
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B14">
-        <v>867</v>
+        <v>442</v>
       </c>
       <c r="C14">
-        <v>96</v>
+        <v>167</v>
       </c>
       <c r="D14">
         <v>26</v>
       </c>
       <c r="E14">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>161</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
       </c>
       <c r="K14" t="s">
         <v>61</v>
@@ -2550,11 +2583,11 @@
       <c r="P14" t="s">
         <v>61</v>
       </c>
-      <c r="Q14" t="s">
-        <v>61</v>
-      </c>
-      <c r="R14" t="s">
-        <v>61</v>
+      <c r="Q14">
+        <v>5</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
       </c>
       <c r="S14" t="s">
         <v>61</v>
@@ -2562,11 +2595,11 @@
       <c r="T14" t="s">
         <v>61</v>
       </c>
-      <c r="U14" t="s">
-        <v>61</v>
-      </c>
-      <c r="V14" t="s">
-        <v>61</v>
+      <c r="U14">
+        <v>5</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
       </c>
       <c r="W14" t="s">
         <v>61</v>
@@ -2574,11 +2607,11 @@
       <c r="X14" t="s">
         <v>61</v>
       </c>
-      <c r="Y14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>61</v>
+      <c r="Y14">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
       </c>
       <c r="AA14" t="s">
         <v>61</v>
@@ -2640,34 +2673,34 @@
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="B15">
-        <v>976</v>
+        <v>185</v>
       </c>
       <c r="C15">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15">
-        <v>168</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
       </c>
       <c r="K15" t="s">
         <v>61</v>
@@ -2687,11 +2720,11 @@
       <c r="P15" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" t="s">
-        <v>61</v>
-      </c>
-      <c r="R15" t="s">
-        <v>61</v>
+      <c r="Q15">
+        <v>6</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
       </c>
       <c r="S15" t="s">
         <v>61</v>
@@ -2699,11 +2732,11 @@
       <c r="T15" t="s">
         <v>61</v>
       </c>
-      <c r="U15" t="s">
-        <v>61</v>
-      </c>
-      <c r="V15" t="s">
-        <v>61</v>
+      <c r="U15">
+        <v>6</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
       </c>
       <c r="W15" t="s">
         <v>61</v>
@@ -2711,11 +2744,11 @@
       <c r="X15" t="s">
         <v>61</v>
       </c>
-      <c r="Y15" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>61</v>
+      <c r="Y15">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
       </c>
       <c r="AA15" t="s">
         <v>61</v>
@@ -2777,28 +2810,28 @@
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16">
-        <v>343</v>
-      </c>
-      <c r="C16">
-        <v>174</v>
-      </c>
-      <c r="D16">
-        <v>10</v>
-      </c>
-      <c r="E16">
-        <v>-9</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" t="s">
+        <v>61</v>
       </c>
       <c r="I16" t="s">
         <v>61</v>
@@ -2848,11 +2881,11 @@
       <c r="X16" t="s">
         <v>61</v>
       </c>
-      <c r="Y16">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>1</v>
+      <c r="Y16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>61</v>
       </c>
       <c r="AA16" t="s">
         <v>61</v>
@@ -2914,28 +2947,28 @@
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="B17">
-        <v>364</v>
+        <v>563</v>
       </c>
       <c r="C17">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="D17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>19</v>
-      </c>
-      <c r="G17">
-        <v>10</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" t="s">
+        <v>61</v>
       </c>
       <c r="I17" t="s">
         <v>61</v>
@@ -2973,11 +3006,11 @@
       <c r="T17" t="s">
         <v>61</v>
       </c>
-      <c r="U17" t="s">
-        <v>61</v>
-      </c>
-      <c r="V17" t="s">
-        <v>61</v>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
       </c>
       <c r="W17" t="s">
         <v>61</v>
@@ -2985,11 +3018,11 @@
       <c r="X17" t="s">
         <v>61</v>
       </c>
-      <c r="Y17" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>61</v>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
       </c>
       <c r="AA17" t="s">
         <v>61</v>
@@ -3051,28 +3084,28 @@
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18">
-        <v>383</v>
-      </c>
-      <c r="C18">
-        <v>37</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>13</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
       </c>
       <c r="I18" t="s">
         <v>61</v>
@@ -3098,11 +3131,11 @@
       <c r="P18" t="s">
         <v>61</v>
       </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18" t="b">
-        <v>1</v>
+      <c r="Q18" t="s">
+        <v>61</v>
+      </c>
+      <c r="R18" t="s">
+        <v>61</v>
       </c>
       <c r="S18" t="s">
         <v>61</v>
@@ -3188,34 +3221,34 @@
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="B19">
-        <v>447</v>
+        <v>119</v>
       </c>
       <c r="C19">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="F19">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>9</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" t="s">
-        <v>61</v>
+        <v>7</v>
+      </c>
+      <c r="G19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19">
+        <v>129</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
       </c>
       <c r="K19" t="s">
         <v>61</v>
@@ -3235,11 +3268,11 @@
       <c r="P19" t="s">
         <v>61</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" t="b">
-        <v>1</v>
+      <c r="Q19" t="s">
+        <v>61</v>
+      </c>
+      <c r="R19" t="s">
+        <v>61</v>
       </c>
       <c r="S19" t="s">
         <v>61</v>
@@ -3325,70 +3358,70 @@
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B20">
-        <v>928</v>
+        <v>119</v>
       </c>
       <c r="C20">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20">
+        <v>130</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" t="s">
+        <v>61</v>
+      </c>
+      <c r="O20" t="s">
+        <v>61</v>
+      </c>
+      <c r="P20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>61</v>
+      </c>
+      <c r="R20" t="s">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
+        <v>61</v>
+      </c>
+      <c r="T20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20">
         <v>2</v>
       </c>
-      <c r="G20">
-        <v>4</v>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>61</v>
-      </c>
-      <c r="J20" t="s">
-        <v>61</v>
-      </c>
-      <c r="K20" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" t="s">
-        <v>61</v>
-      </c>
-      <c r="M20" t="s">
-        <v>61</v>
-      </c>
-      <c r="N20" t="s">
-        <v>61</v>
-      </c>
-      <c r="O20" t="s">
-        <v>61</v>
-      </c>
-      <c r="P20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="R20" t="b">
-        <v>1</v>
-      </c>
-      <c r="S20" t="s">
-        <v>61</v>
-      </c>
-      <c r="T20" t="s">
-        <v>61</v>
-      </c>
-      <c r="U20" t="s">
-        <v>61</v>
-      </c>
-      <c r="V20" t="s">
-        <v>61</v>
+      <c r="V20" t="b">
+        <v>1</v>
       </c>
       <c r="W20" t="s">
         <v>61</v>
@@ -3462,28 +3495,28 @@
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21">
-        <v>790</v>
-      </c>
-      <c r="C21">
-        <v>141</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>-9</v>
-      </c>
-      <c r="F21">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>14</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
+        <v>112</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
+        <v>61</v>
       </c>
       <c r="I21" t="s">
         <v>61</v>
@@ -3599,43 +3632,43 @@
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B22">
-        <v>875</v>
+        <v>441</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="D22">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>-9</v>
       </c>
       <c r="F22">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>7</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>61</v>
-      </c>
-      <c r="J22" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" t="s">
-        <v>61</v>
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22">
+        <v>113</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="N22" t="s">
         <v>61</v>
@@ -3652,11 +3685,11 @@
       <c r="R22" t="s">
         <v>61</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22" t="b">
-        <v>1</v>
+      <c r="S22" t="s">
+        <v>61</v>
+      </c>
+      <c r="T22" t="s">
+        <v>61</v>
       </c>
       <c r="U22">
         <v>1</v>
@@ -3670,11 +3703,11 @@
       <c r="X22" t="s">
         <v>61</v>
       </c>
-      <c r="Y22" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>61</v>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
       </c>
       <c r="AA22" t="s">
         <v>61</v>
@@ -3682,11 +3715,11 @@
       <c r="AB22" t="s">
         <v>61</v>
       </c>
-      <c r="AC22" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>61</v>
+      <c r="AC22">
+        <v>6</v>
+      </c>
+      <c r="AD22" t="b">
+        <v>1</v>
       </c>
       <c r="AE22" t="s">
         <v>61</v>
@@ -3736,28 +3769,28 @@
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B23">
-        <v>890</v>
+        <v>88</v>
       </c>
       <c r="C23">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>15</v>
-      </c>
-      <c r="G23">
-        <v>6</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>61</v>
       </c>
       <c r="I23" t="s">
         <v>61</v>
@@ -3783,11 +3816,11 @@
       <c r="P23" t="s">
         <v>61</v>
       </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23" t="b">
-        <v>1</v>
+      <c r="Q23" t="s">
+        <v>61</v>
+      </c>
+      <c r="R23" t="s">
+        <v>61</v>
       </c>
       <c r="S23" t="s">
         <v>61</v>
@@ -3837,11 +3870,11 @@
       <c r="AH23" t="s">
         <v>61</v>
       </c>
-      <c r="AI23">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
+      <c r="AI23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>61</v>
       </c>
       <c r="AK23" t="s">
         <v>61</v>
@@ -3873,34 +3906,34 @@
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B24">
-        <v>401</v>
+        <v>867</v>
       </c>
       <c r="C24">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
-      <c r="I24" t="s">
-        <v>61</v>
-      </c>
-      <c r="J24" t="s">
-        <v>61</v>
+      <c r="I24">
+        <v>161</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
       </c>
       <c r="K24" t="s">
         <v>61</v>
@@ -3911,20 +3944,20 @@
       <c r="M24" t="s">
         <v>61</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24">
-        <v>10000</v>
-      </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24" t="b">
-        <v>1</v>
+      <c r="N24" t="s">
+        <v>61</v>
+      </c>
+      <c r="O24" t="s">
+        <v>61</v>
+      </c>
+      <c r="P24" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>61</v>
+      </c>
+      <c r="R24" t="s">
+        <v>61</v>
       </c>
       <c r="S24" t="s">
         <v>61</v>
@@ -3932,11 +3965,11 @@
       <c r="T24" t="s">
         <v>61</v>
       </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24" t="b">
-        <v>1</v>
+      <c r="U24" t="s">
+        <v>61</v>
+      </c>
+      <c r="V24" t="s">
+        <v>61</v>
       </c>
       <c r="W24" t="s">
         <v>61</v>
@@ -3974,11 +4007,11 @@
       <c r="AH24" t="s">
         <v>61</v>
       </c>
-      <c r="AI24">
-        <v>11</v>
-      </c>
-      <c r="AJ24" t="b">
-        <v>1</v>
+      <c r="AI24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>61</v>
       </c>
       <c r="AK24" t="s">
         <v>61</v>
@@ -3995,11 +4028,11 @@
       <c r="AO24" t="s">
         <v>61</v>
       </c>
-      <c r="AP24">
-        <v>1</v>
-      </c>
-      <c r="AQ24" t="b">
-        <v>1</v>
+      <c r="AP24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>61</v>
       </c>
       <c r="AR24" t="s">
         <v>61</v>
@@ -4010,34 +4043,34 @@
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B25">
-        <v>676</v>
+        <v>976</v>
       </c>
       <c r="C25">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D25">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F25">
-        <v>17</v>
-      </c>
-      <c r="G25">
         <v>12</v>
       </c>
-      <c r="H25" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>61</v>
-      </c>
-      <c r="J25" t="s">
-        <v>61</v>
+      <c r="G25" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25">
+        <v>168</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
       </c>
       <c r="K25" t="s">
         <v>61</v>
@@ -4057,11 +4090,11 @@
       <c r="P25" t="s">
         <v>61</v>
       </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25" t="b">
-        <v>1</v>
+      <c r="Q25" t="s">
+        <v>61</v>
+      </c>
+      <c r="R25" t="s">
+        <v>61</v>
       </c>
       <c r="S25" t="s">
         <v>61</v>
@@ -4069,11 +4102,11 @@
       <c r="T25" t="s">
         <v>61</v>
       </c>
-      <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25" t="b">
-        <v>1</v>
+      <c r="U25" t="s">
+        <v>61</v>
+      </c>
+      <c r="V25" t="s">
+        <v>61</v>
       </c>
       <c r="W25" t="s">
         <v>61</v>
@@ -4087,11 +4120,11 @@
       <c r="Z25" t="s">
         <v>61</v>
       </c>
-      <c r="AA25">
-        <v>55</v>
-      </c>
-      <c r="AB25" t="b">
-        <v>1</v>
+      <c r="AA25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>61</v>
       </c>
       <c r="AC25" t="s">
         <v>61</v>
@@ -4147,29 +4180,29 @@
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B26">
-        <v>626</v>
+        <v>343</v>
       </c>
       <c r="C26">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E26">
+        <v>-9</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
-      <c r="F26">
-        <v>4</v>
-      </c>
-      <c r="G26">
-        <v>6</v>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
-      </c>
       <c r="I26" t="s">
         <v>61</v>
       </c>
@@ -4194,11 +4227,11 @@
       <c r="P26" t="s">
         <v>61</v>
       </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26" t="b">
-        <v>1</v>
+      <c r="Q26" t="s">
+        <v>61</v>
+      </c>
+      <c r="R26" t="s">
+        <v>61</v>
       </c>
       <c r="S26" t="s">
         <v>61</v>
@@ -4206,11 +4239,11 @@
       <c r="T26" t="s">
         <v>61</v>
       </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26" t="b">
-        <v>1</v>
+      <c r="U26" t="s">
+        <v>61</v>
+      </c>
+      <c r="V26" t="s">
+        <v>61</v>
       </c>
       <c r="W26" t="s">
         <v>61</v>
@@ -4284,43 +4317,43 @@
     </row>
     <row r="27" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B27">
-        <v>613</v>
+        <v>364</v>
       </c>
       <c r="C27">
-        <v>192</v>
+        <v>117</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27" t="b">
         <v>0</v>
       </c>
-      <c r="H27" t="b">
-        <v>1</v>
-      </c>
       <c r="I27" t="s">
         <v>61</v>
       </c>
       <c r="J27" t="s">
         <v>61</v>
       </c>
-      <c r="K27">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
+      <c r="K27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" t="s">
+        <v>61</v>
       </c>
       <c r="M27" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="N27" t="s">
         <v>61</v>
@@ -4331,11 +4364,11 @@
       <c r="P27" t="s">
         <v>61</v>
       </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27" t="b">
-        <v>1</v>
+      <c r="Q27" t="s">
+        <v>61</v>
+      </c>
+      <c r="R27" t="s">
+        <v>61</v>
       </c>
       <c r="S27" t="s">
         <v>61</v>
@@ -4343,11 +4376,11 @@
       <c r="T27" t="s">
         <v>61</v>
       </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27" t="b">
-        <v>1</v>
+      <c r="U27" t="s">
+        <v>61</v>
+      </c>
+      <c r="V27" t="s">
+        <v>61</v>
       </c>
       <c r="W27" t="s">
         <v>61</v>
@@ -4355,11 +4388,11 @@
       <c r="X27" t="s">
         <v>61</v>
       </c>
-      <c r="Y27">
-        <v>1</v>
-      </c>
-      <c r="Z27" t="b">
-        <v>1</v>
+      <c r="Y27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>61</v>
       </c>
       <c r="AA27" t="s">
         <v>61</v>
@@ -4379,11 +4412,11 @@
       <c r="AF27" t="s">
         <v>61</v>
       </c>
-      <c r="AG27">
-        <v>6</v>
-      </c>
-      <c r="AH27" t="b">
-        <v>1</v>
+      <c r="AG27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>61</v>
       </c>
       <c r="AI27" t="s">
         <v>61</v>
@@ -4421,25 +4454,25 @@
     </row>
     <row r="28" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B28">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="C28">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -4468,11 +4501,11 @@
       <c r="P28" t="s">
         <v>61</v>
       </c>
-      <c r="Q28" t="s">
-        <v>61</v>
-      </c>
-      <c r="R28" t="s">
-        <v>61</v>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
       </c>
       <c r="S28" t="s">
         <v>61</v>
@@ -4486,11 +4519,11 @@
       <c r="V28" t="s">
         <v>61</v>
       </c>
-      <c r="W28">
-        <v>50</v>
-      </c>
-      <c r="X28" t="b">
-        <v>1</v>
+      <c r="W28" t="s">
+        <v>61</v>
+      </c>
+      <c r="X28" t="s">
+        <v>61</v>
       </c>
       <c r="Y28" t="s">
         <v>61</v>
@@ -4558,28 +4591,28 @@
     </row>
     <row r="29" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B29">
-        <v>211</v>
+        <v>447</v>
       </c>
       <c r="C29">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G29">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="s">
         <v>61</v>
@@ -4629,11 +4662,11 @@
       <c r="X29" t="s">
         <v>61</v>
       </c>
-      <c r="Y29">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="b">
-        <v>1</v>
+      <c r="Y29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>61</v>
       </c>
       <c r="AA29" t="s">
         <v>61</v>
@@ -4665,20 +4698,20 @@
       <c r="AJ29" t="s">
         <v>61</v>
       </c>
-      <c r="AK29">
-        <v>25</v>
-      </c>
-      <c r="AL29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM29">
-        <v>25</v>
-      </c>
-      <c r="AN29">
-        <v>25</v>
-      </c>
-      <c r="AO29">
-        <v>25</v>
+      <c r="AK29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>61</v>
       </c>
       <c r="AP29" t="s">
         <v>61</v>
@@ -4686,37 +4719,37 @@
       <c r="AQ29" t="s">
         <v>61</v>
       </c>
-      <c r="AR29">
-        <v>20</v>
-      </c>
-      <c r="AS29" t="b">
-        <v>1</v>
+      <c r="AR29" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B30">
-        <v>670</v>
+        <v>928</v>
       </c>
       <c r="C30">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="D30">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="s">
         <v>61</v>
@@ -4754,11 +4787,11 @@
       <c r="T30" t="s">
         <v>61</v>
       </c>
-      <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="V30" t="b">
-        <v>1</v>
+      <c r="U30" t="s">
+        <v>61</v>
+      </c>
+      <c r="V30" t="s">
+        <v>61</v>
       </c>
       <c r="W30" t="s">
         <v>61</v>
@@ -4832,25 +4865,25 @@
     </row>
     <row r="31" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B31">
-        <v>239</v>
+        <v>790</v>
       </c>
       <c r="C31">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="D31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="F31">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -4879,11 +4912,11 @@
       <c r="P31" t="s">
         <v>61</v>
       </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31" t="b">
-        <v>1</v>
+      <c r="Q31" t="s">
+        <v>61</v>
+      </c>
+      <c r="R31" t="s">
+        <v>61</v>
       </c>
       <c r="S31" t="s">
         <v>61</v>
@@ -4891,11 +4924,11 @@
       <c r="T31" t="s">
         <v>61</v>
       </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31" t="b">
-        <v>1</v>
+      <c r="U31" t="s">
+        <v>61</v>
+      </c>
+      <c r="V31" t="s">
+        <v>61</v>
       </c>
       <c r="W31" t="s">
         <v>61</v>
@@ -4903,11 +4936,11 @@
       <c r="X31" t="s">
         <v>61</v>
       </c>
-      <c r="Y31">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>1</v>
+      <c r="Y31" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>61</v>
       </c>
       <c r="AA31" t="s">
         <v>61</v>
@@ -4927,11 +4960,11 @@
       <c r="AF31" t="s">
         <v>61</v>
       </c>
-      <c r="AG31">
-        <v>8</v>
-      </c>
-      <c r="AH31" t="b">
-        <v>1</v>
+      <c r="AG31" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>61</v>
       </c>
       <c r="AI31" t="s">
         <v>61</v>
@@ -4969,25 +5002,25 @@
     </row>
     <row r="32" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B32">
-        <v>347</v>
+        <v>875</v>
       </c>
       <c r="C32">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E32">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -5016,23 +5049,23 @@
       <c r="P32" t="s">
         <v>61</v>
       </c>
-      <c r="Q32">
-        <v>1</v>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="s">
-        <v>61</v>
-      </c>
-      <c r="T32" t="s">
-        <v>61</v>
-      </c>
-      <c r="U32" t="s">
-        <v>61</v>
-      </c>
-      <c r="V32" t="s">
-        <v>61</v>
+      <c r="Q32" t="s">
+        <v>61</v>
+      </c>
+      <c r="R32" t="s">
+        <v>61</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
       </c>
       <c r="W32" t="s">
         <v>61</v>
@@ -5058,17 +5091,17 @@
       <c r="AD32" t="s">
         <v>61</v>
       </c>
-      <c r="AE32">
-        <v>9</v>
-      </c>
-      <c r="AF32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG32">
-        <v>9</v>
-      </c>
-      <c r="AH32" t="b">
-        <v>1</v>
+      <c r="AE32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>61</v>
       </c>
       <c r="AI32" t="s">
         <v>61</v>
@@ -5106,28 +5139,28 @@
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B33">
-        <v>558</v>
+        <v>890</v>
       </c>
       <c r="C33">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="D33">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="s">
         <v>61</v>
@@ -5195,23 +5228,23 @@
       <c r="AD33" t="s">
         <v>61</v>
       </c>
-      <c r="AE33">
-        <v>7</v>
-      </c>
-      <c r="AF33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG33">
-        <v>3</v>
-      </c>
-      <c r="AH33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>61</v>
+      <c r="AE33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI33">
+        <v>8</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
       </c>
       <c r="AK33" t="s">
         <v>61</v>
@@ -5243,25 +5276,25 @@
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B34">
-        <v>995</v>
+        <v>401</v>
       </c>
       <c r="C34">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="D34">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E34">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -5281,20 +5314,20 @@
       <c r="M34" t="s">
         <v>61</v>
       </c>
-      <c r="N34" t="s">
-        <v>61</v>
-      </c>
-      <c r="O34" t="s">
-        <v>61</v>
-      </c>
-      <c r="P34" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>61</v>
-      </c>
-      <c r="R34" t="s">
-        <v>61</v>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
+        <v>10000</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
       </c>
       <c r="S34" t="s">
         <v>61</v>
@@ -5302,11 +5335,11 @@
       <c r="T34" t="s">
         <v>61</v>
       </c>
-      <c r="U34" t="s">
-        <v>61</v>
-      </c>
-      <c r="V34" t="s">
-        <v>61</v>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
       </c>
       <c r="W34" t="s">
         <v>61</v>
@@ -5344,11 +5377,11 @@
       <c r="AH34" t="s">
         <v>61</v>
       </c>
-      <c r="AI34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>61</v>
+      <c r="AI34">
+        <v>11</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
       </c>
       <c r="AK34" t="s">
         <v>61</v>
@@ -5365,11 +5398,11 @@
       <c r="AO34" t="s">
         <v>61</v>
       </c>
-      <c r="AP34" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ34" t="s">
-        <v>61</v>
+      <c r="AP34">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="b">
+        <v>1</v>
       </c>
       <c r="AR34" t="s">
         <v>61</v>
@@ -5380,28 +5413,28 @@
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35">
-        <v>522</v>
-      </c>
-      <c r="C35">
-        <v>148</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-      <c r="F35">
-        <v>13</v>
-      </c>
-      <c r="G35">
-        <v>11</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
+        <v>115</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" t="s">
+        <v>61</v>
       </c>
       <c r="I35" t="s">
         <v>61</v>
@@ -5517,28 +5550,28 @@
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B36">
-        <v>599</v>
+        <v>676</v>
       </c>
       <c r="C36">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="s">
         <v>61</v>
@@ -5576,11 +5609,11 @@
       <c r="T36" t="s">
         <v>61</v>
       </c>
-      <c r="U36" t="s">
-        <v>61</v>
-      </c>
-      <c r="V36" t="s">
-        <v>61</v>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36" t="b">
+        <v>1</v>
       </c>
       <c r="W36" t="s">
         <v>61</v>
@@ -5594,11 +5627,11 @@
       <c r="Z36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>61</v>
+      <c r="AA36">
+        <v>55</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>1</v>
       </c>
       <c r="AC36" t="s">
         <v>61</v>
@@ -5654,25 +5687,25 @@
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B37">
-        <v>795</v>
+        <v>626</v>
       </c>
       <c r="C37">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="D37">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E37">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -5713,11 +5746,11 @@
       <c r="T37" t="s">
         <v>61</v>
       </c>
-      <c r="U37" t="s">
-        <v>61</v>
-      </c>
-      <c r="V37" t="s">
-        <v>61</v>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37" t="b">
+        <v>1</v>
       </c>
       <c r="W37" t="s">
         <v>61</v>
@@ -5725,11 +5758,11 @@
       <c r="X37" t="s">
         <v>61</v>
       </c>
-      <c r="Y37" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>61</v>
+      <c r="Y37">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
       </c>
       <c r="AA37" t="s">
         <v>61</v>
@@ -5791,106 +5824,106 @@
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B38">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>98</v>
+      </c>
+      <c r="N38" t="s">
+        <v>61</v>
+      </c>
+      <c r="O38" t="s">
+        <v>61</v>
+      </c>
+      <c r="P38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="s">
+        <v>61</v>
+      </c>
+      <c r="T38" t="s">
+        <v>61</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" t="s">
+        <v>61</v>
+      </c>
+      <c r="X38" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y38">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG38">
         <v>6</v>
       </c>
-      <c r="F38">
-        <v>7</v>
-      </c>
-      <c r="G38">
-        <v>15</v>
-      </c>
-      <c r="H38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>61</v>
-      </c>
-      <c r="J38" t="s">
-        <v>61</v>
-      </c>
-      <c r="K38" t="s">
-        <v>61</v>
-      </c>
-      <c r="L38" t="s">
-        <v>61</v>
-      </c>
-      <c r="M38" t="s">
-        <v>61</v>
-      </c>
-      <c r="N38" t="s">
-        <v>61</v>
-      </c>
-      <c r="O38" t="s">
-        <v>61</v>
-      </c>
-      <c r="P38" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q38">
-        <v>1</v>
-      </c>
-      <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>61</v>
-      </c>
-      <c r="T38" t="s">
-        <v>61</v>
-      </c>
-      <c r="U38" t="s">
-        <v>61</v>
-      </c>
-      <c r="V38" t="s">
-        <v>61</v>
-      </c>
-      <c r="W38" t="s">
-        <v>61</v>
-      </c>
-      <c r="X38" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>61</v>
+      <c r="AH38" t="b">
+        <v>1</v>
       </c>
       <c r="AI38" t="s">
         <v>61</v>
@@ -5928,138 +5961,1645 @@
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B39">
+        <v>299</v>
+      </c>
+      <c r="C39">
+        <v>196</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>15</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" t="s">
+        <v>61</v>
+      </c>
+      <c r="O39" t="s">
+        <v>61</v>
+      </c>
+      <c r="P39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>61</v>
+      </c>
+      <c r="R39" t="s">
+        <v>61</v>
+      </c>
+      <c r="S39" t="s">
+        <v>61</v>
+      </c>
+      <c r="T39" t="s">
+        <v>61</v>
+      </c>
+      <c r="U39" t="s">
+        <v>61</v>
+      </c>
+      <c r="V39" t="s">
+        <v>61</v>
+      </c>
+      <c r="W39">
+        <v>50</v>
+      </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40">
+        <v>211</v>
+      </c>
+      <c r="C40">
+        <v>151</v>
+      </c>
+      <c r="D40">
+        <v>15</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40">
+        <v>13</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" t="s">
+        <v>61</v>
+      </c>
+      <c r="K40" t="s">
+        <v>61</v>
+      </c>
+      <c r="L40" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" t="s">
+        <v>61</v>
+      </c>
+      <c r="O40" t="s">
+        <v>61</v>
+      </c>
+      <c r="P40" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="s">
+        <v>61</v>
+      </c>
+      <c r="T40" t="s">
+        <v>61</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="W40" t="s">
+        <v>61</v>
+      </c>
+      <c r="X40" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK40">
+        <v>25</v>
+      </c>
+      <c r="AL40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM40">
+        <v>25</v>
+      </c>
+      <c r="AN40">
+        <v>25</v>
+      </c>
+      <c r="AO40">
+        <v>25</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR40">
+        <v>20</v>
+      </c>
+      <c r="AS40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41">
+        <v>670</v>
+      </c>
+      <c r="C41">
+        <v>187</v>
+      </c>
+      <c r="D41">
+        <v>22</v>
+      </c>
+      <c r="E41">
+        <v>-4</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41" t="s">
+        <v>61</v>
+      </c>
+      <c r="L41" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" t="s">
+        <v>61</v>
+      </c>
+      <c r="N41" t="s">
+        <v>61</v>
+      </c>
+      <c r="O41" t="s">
+        <v>61</v>
+      </c>
+      <c r="P41" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="s">
+        <v>61</v>
+      </c>
+      <c r="T41" t="s">
+        <v>61</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" t="s">
+        <v>61</v>
+      </c>
+      <c r="X41" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42">
+        <v>239</v>
+      </c>
+      <c r="C42">
+        <v>37</v>
+      </c>
+      <c r="D42">
+        <v>32</v>
+      </c>
+      <c r="E42">
+        <v>-1</v>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" t="s">
+        <v>61</v>
+      </c>
+      <c r="K42" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" t="s">
+        <v>61</v>
+      </c>
+      <c r="N42" t="s">
+        <v>61</v>
+      </c>
+      <c r="O42" t="s">
+        <v>61</v>
+      </c>
+      <c r="P42" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
+      <c r="S42" t="s">
+        <v>61</v>
+      </c>
+      <c r="T42" t="s">
+        <v>61</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="W42" t="s">
+        <v>61</v>
+      </c>
+      <c r="X42" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y42">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG42">
+        <v>8</v>
+      </c>
+      <c r="AH42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43">
+        <v>347</v>
+      </c>
+      <c r="C43">
+        <v>130</v>
+      </c>
+      <c r="D43">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>-7</v>
+      </c>
+      <c r="F43">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>19</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K43" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" t="s">
+        <v>61</v>
+      </c>
+      <c r="N43" t="s">
+        <v>61</v>
+      </c>
+      <c r="O43" t="s">
+        <v>61</v>
+      </c>
+      <c r="P43" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="s">
+        <v>61</v>
+      </c>
+      <c r="T43" t="s">
+        <v>61</v>
+      </c>
+      <c r="U43" t="s">
+        <v>61</v>
+      </c>
+      <c r="V43" t="s">
+        <v>61</v>
+      </c>
+      <c r="W43" t="s">
+        <v>61</v>
+      </c>
+      <c r="X43" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE43">
+        <v>9</v>
+      </c>
+      <c r="AF43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43">
+        <v>9</v>
+      </c>
+      <c r="AH43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR43" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44">
+        <v>558</v>
+      </c>
+      <c r="C44">
+        <v>76</v>
+      </c>
+      <c r="D44">
+        <v>21</v>
+      </c>
+      <c r="E44">
+        <v>-8</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>11</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" t="s">
+        <v>61</v>
+      </c>
+      <c r="K44" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" t="s">
+        <v>61</v>
+      </c>
+      <c r="O44" t="s">
+        <v>61</v>
+      </c>
+      <c r="P44" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="s">
+        <v>61</v>
+      </c>
+      <c r="T44" t="s">
+        <v>61</v>
+      </c>
+      <c r="U44" t="s">
+        <v>61</v>
+      </c>
+      <c r="V44" t="s">
+        <v>61</v>
+      </c>
+      <c r="W44" t="s">
+        <v>61</v>
+      </c>
+      <c r="X44" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE44">
+        <v>7</v>
+      </c>
+      <c r="AF44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44">
+        <v>3</v>
+      </c>
+      <c r="AH44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45">
+        <v>995</v>
+      </c>
+      <c r="C45">
+        <v>73</v>
+      </c>
+      <c r="D45">
+        <v>16</v>
+      </c>
+      <c r="E45">
+        <v>-7</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45">
+        <v>18</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" t="s">
+        <v>61</v>
+      </c>
+      <c r="N45" t="s">
+        <v>61</v>
+      </c>
+      <c r="O45" t="s">
+        <v>61</v>
+      </c>
+      <c r="P45" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>61</v>
+      </c>
+      <c r="R45" t="s">
+        <v>61</v>
+      </c>
+      <c r="S45" t="s">
+        <v>61</v>
+      </c>
+      <c r="T45" t="s">
+        <v>61</v>
+      </c>
+      <c r="U45" t="s">
+        <v>61</v>
+      </c>
+      <c r="V45" t="s">
+        <v>61</v>
+      </c>
+      <c r="W45" t="s">
+        <v>61</v>
+      </c>
+      <c r="X45" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR45" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS45" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46">
+        <v>522</v>
+      </c>
+      <c r="C46">
+        <v>148</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>13</v>
+      </c>
+      <c r="G46">
+        <v>11</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" t="s">
+        <v>61</v>
+      </c>
+      <c r="K46" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" t="s">
+        <v>61</v>
+      </c>
+      <c r="O46" t="s">
+        <v>61</v>
+      </c>
+      <c r="P46" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>61</v>
+      </c>
+      <c r="R46" t="s">
+        <v>61</v>
+      </c>
+      <c r="S46" t="s">
+        <v>61</v>
+      </c>
+      <c r="T46" t="s">
+        <v>61</v>
+      </c>
+      <c r="U46" t="s">
+        <v>61</v>
+      </c>
+      <c r="V46" t="s">
+        <v>61</v>
+      </c>
+      <c r="W46" t="s">
+        <v>61</v>
+      </c>
+      <c r="X46" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR46" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47">
+        <v>599</v>
+      </c>
+      <c r="C47">
+        <v>159</v>
+      </c>
+      <c r="D47">
+        <v>20</v>
+      </c>
+      <c r="E47">
+        <v>10</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>61</v>
+      </c>
+      <c r="J47" t="s">
+        <v>61</v>
+      </c>
+      <c r="K47" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" t="s">
+        <v>61</v>
+      </c>
+      <c r="M47" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" t="s">
+        <v>61</v>
+      </c>
+      <c r="O47" t="s">
+        <v>61</v>
+      </c>
+      <c r="P47" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="s">
+        <v>61</v>
+      </c>
+      <c r="T47" t="s">
+        <v>61</v>
+      </c>
+      <c r="U47" t="s">
+        <v>61</v>
+      </c>
+      <c r="V47" t="s">
+        <v>61</v>
+      </c>
+      <c r="W47" t="s">
+        <v>61</v>
+      </c>
+      <c r="X47" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR47" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS47" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48">
+        <v>795</v>
+      </c>
+      <c r="C48">
+        <v>151</v>
+      </c>
+      <c r="D48">
+        <v>22</v>
+      </c>
+      <c r="E48">
+        <v>-4</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>61</v>
+      </c>
+      <c r="J48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" t="s">
+        <v>61</v>
+      </c>
+      <c r="M48" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O48" t="s">
+        <v>61</v>
+      </c>
+      <c r="P48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" t="s">
+        <v>61</v>
+      </c>
+      <c r="T48" t="s">
+        <v>61</v>
+      </c>
+      <c r="U48" t="s">
+        <v>61</v>
+      </c>
+      <c r="V48" t="s">
+        <v>61</v>
+      </c>
+      <c r="W48" t="s">
+        <v>61</v>
+      </c>
+      <c r="X48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49">
+        <v>624</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>15</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" t="s">
+        <v>61</v>
+      </c>
+      <c r="K49" t="s">
+        <v>61</v>
+      </c>
+      <c r="L49" t="s">
+        <v>61</v>
+      </c>
+      <c r="M49" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" t="s">
+        <v>61</v>
+      </c>
+      <c r="O49" t="s">
+        <v>61</v>
+      </c>
+      <c r="P49" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="s">
+        <v>61</v>
+      </c>
+      <c r="T49" t="s">
+        <v>61</v>
+      </c>
+      <c r="U49" t="s">
+        <v>61</v>
+      </c>
+      <c r="V49" t="s">
+        <v>61</v>
+      </c>
+      <c r="W49" t="s">
+        <v>61</v>
+      </c>
+      <c r="X49" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:45" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50">
         <v>647</v>
       </c>
-      <c r="C39">
+      <c r="C50">
         <v>101</v>
       </c>
-      <c r="D39">
+      <c r="D50">
         <v>12</v>
       </c>
-      <c r="E39">
+      <c r="E50">
         <v>-10</v>
       </c>
-      <c r="F39">
+      <c r="F50">
         <v>14</v>
       </c>
-      <c r="G39">
+      <c r="G50">
         <v>20</v>
       </c>
-      <c r="H39" t="b">
+      <c r="H50" t="b">
         <v>0</v>
       </c>
-      <c r="I39" t="s">
-        <v>61</v>
-      </c>
-      <c r="J39" t="s">
-        <v>61</v>
-      </c>
-      <c r="K39" t="s">
-        <v>61</v>
-      </c>
-      <c r="L39" t="s">
-        <v>61</v>
-      </c>
-      <c r="M39" t="s">
-        <v>61</v>
-      </c>
-      <c r="N39" t="s">
-        <v>61</v>
-      </c>
-      <c r="O39" t="s">
-        <v>61</v>
-      </c>
-      <c r="P39" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="s">
-        <v>61</v>
-      </c>
-      <c r="T39" t="s">
-        <v>61</v>
-      </c>
-      <c r="U39" t="s">
-        <v>61</v>
-      </c>
-      <c r="V39" t="s">
-        <v>61</v>
-      </c>
-      <c r="W39" t="s">
-        <v>61</v>
-      </c>
-      <c r="X39" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AO39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AP39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR39" t="s">
-        <v>61</v>
-      </c>
-      <c r="AS39" t="s">
+      <c r="I50" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" t="s">
+        <v>61</v>
+      </c>
+      <c r="K50" t="s">
+        <v>61</v>
+      </c>
+      <c r="L50" t="s">
+        <v>61</v>
+      </c>
+      <c r="M50" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" t="s">
+        <v>61</v>
+      </c>
+      <c r="O50" t="s">
+        <v>61</v>
+      </c>
+      <c r="P50" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
+      <c r="S50" t="s">
+        <v>61</v>
+      </c>
+      <c r="T50" t="s">
+        <v>61</v>
+      </c>
+      <c r="U50" t="s">
+        <v>61</v>
+      </c>
+      <c r="V50" t="s">
+        <v>61</v>
+      </c>
+      <c r="W50" t="s">
+        <v>61</v>
+      </c>
+      <c r="X50" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR50" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS50" t="s">
         <v>61</v>
       </c>
     </row>
